--- a/Financial Analysis/PSFE.xlsx
+++ b/Financial Analysis/PSFE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C492838-85B0-45B5-82C2-D15D738F4161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F606CF-5539-4B26-9D8F-99E262775406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{6F8D5EDB-60E6-4055-AE62-151FC6B3FA19}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{6F8D5EDB-60E6-4055-AE62-151FC6B3FA19}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>PSFE</t>
   </si>
@@ -223,7 +223,13 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>early cash flow matters a lot</t>
+  </si>
+  <si>
+    <t>maybe good to do cash flow statement</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -323,14 +329,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -347,7 +353,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13876020" y="0"/>
+          <a:off x="15087600" y="0"/>
           <a:ext cx="0" cy="6111240"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -746,17 +752,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>14.96</v>
+        <v>13.53</v>
       </c>
       <c r="E3" s="3">
-        <v>45751</v>
+        <v>45888</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45888</v>
       </c>
       <c r="G3" s="3">
-        <v>45784</v>
+        <v>45967</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -764,11 +770,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>59.9</f>
-        <v>59.9</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -777,7 +783,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>896.10400000000004</v>
+        <v>795.56399999999996</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -785,10 +791,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <v>216.7</v>
+        <f>234.3</f>
+        <v>234.3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -796,11 +803,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>10.2+2353.4</f>
-        <v>2363.6</v>
+        <f>10.2+2374.4</f>
+        <v>2384.6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -809,7 +816,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-2146.9</v>
+        <v>-2150.2999999999997</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -818,7 +825,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>3043.0039999999999</v>
+        <v>2945.8639999999996</v>
       </c>
     </row>
   </sheetData>
@@ -1032,20 +1039,18 @@
         <v>420.09999999999985</v>
       </c>
       <c r="W3" s="8">
-        <f>S3*1.02</f>
-        <v>426.05399999999997</v>
+        <v>401</v>
       </c>
       <c r="X3" s="8">
-        <f>T3*1.01</f>
-        <v>444.29899999999998</v>
+        <v>428.2</v>
       </c>
       <c r="Y3" s="8">
-        <f t="shared" ref="Y3:Z3" si="0">U3*1.02</f>
-        <v>435.64200000000005</v>
+        <f>U3*0.99</f>
+        <v>422.82900000000001</v>
       </c>
       <c r="Z3" s="8">
-        <f t="shared" si="0"/>
-        <v>428.50199999999984</v>
+        <f>V3*1.01</f>
+        <v>424.30099999999987</v>
       </c>
       <c r="AA3" s="8"/>
       <c r="AB3" s="8">
@@ -1074,47 +1079,47 @@
       </c>
       <c r="AI3" s="8">
         <f>SUM(W3:Z3)</f>
-        <v>1734.4969999999998</v>
+        <v>1676.33</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.02</f>
-        <v>1769.1869399999998</v>
+        <v>1709.8565999999998</v>
       </c>
       <c r="AK3" s="8">
-        <f t="shared" ref="AK3:AS3" si="1">AJ3*1.02</f>
-        <v>1804.5706787999998</v>
+        <f t="shared" ref="AK3:AS3" si="0">AJ3*1.02</f>
+        <v>1744.0537319999999</v>
       </c>
       <c r="AL3" s="8">
-        <f t="shared" si="1"/>
-        <v>1840.6620923759997</v>
+        <f t="shared" si="0"/>
+        <v>1778.9348066399998</v>
       </c>
       <c r="AM3" s="8">
-        <f t="shared" si="1"/>
-        <v>1877.4753342235197</v>
+        <f t="shared" si="0"/>
+        <v>1814.5135027727999</v>
       </c>
       <c r="AN3" s="8">
-        <f t="shared" si="1"/>
-        <v>1915.02484090799</v>
+        <f t="shared" si="0"/>
+        <v>1850.8037728282559</v>
       </c>
       <c r="AO3" s="8">
-        <f t="shared" si="1"/>
-        <v>1953.3253377261499</v>
+        <f>AN3*1.01</f>
+        <v>1869.3118105565384</v>
       </c>
       <c r="AP3" s="8">
-        <f t="shared" si="1"/>
-        <v>1992.3918444806729</v>
+        <f t="shared" ref="AP3:AS3" si="1">AO3*1.01</f>
+        <v>1888.0049286621038</v>
       </c>
       <c r="AQ3" s="8">
         <f t="shared" si="1"/>
-        <v>2032.2396813702865</v>
+        <v>1906.8849779487248</v>
       </c>
       <c r="AR3" s="8">
         <f t="shared" si="1"/>
-        <v>2072.8844749976925</v>
+        <v>1925.953827728212</v>
       </c>
       <c r="AS3" s="8">
         <f t="shared" si="1"/>
-        <v>2114.3421644976465</v>
+        <v>1945.2133660054942</v>
       </c>
     </row>
     <row r="4" spans="2:162" x14ac:dyDescent="0.3">
@@ -1183,20 +1188,18 @@
         <v>183.49999999999991</v>
       </c>
       <c r="W4" s="5">
-        <f>W3-W5</f>
-        <v>187.46375999999998</v>
+        <v>174.2</v>
       </c>
       <c r="X4" s="5">
-        <f t="shared" ref="X4:Z4" si="2">X3-X5</f>
-        <v>195.49155999999996</v>
+        <v>190.2</v>
       </c>
       <c r="Y4" s="5">
-        <f t="shared" si="2"/>
-        <v>191.68248</v>
+        <f t="shared" ref="X4:Z4" si="2">Y3-Y5</f>
+        <v>186.04475999999997</v>
       </c>
       <c r="Z4" s="5">
         <f t="shared" si="2"/>
-        <v>188.5408799999999</v>
+        <v>186.69243999999992</v>
       </c>
       <c r="AB4" s="5">
         <v>390.7</v>
@@ -1223,48 +1226,48 @@
         <v>715.8</v>
       </c>
       <c r="AI4" s="5">
-        <f t="shared" ref="AI4:AO4" si="3">AI3-AI5</f>
-        <v>693.79880000000003</v>
+        <f>SUM(W4:Z4)</f>
+        <v>737.13719999999989</v>
       </c>
       <c r="AJ4" s="5">
-        <f t="shared" si="3"/>
-        <v>760.75038419999998</v>
+        <f t="shared" ref="AJ4:AO4" si="3">AJ3-AJ5</f>
+        <v>735.238338</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="3"/>
-        <v>757.91968509599997</v>
+        <v>732.50256744000001</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="3"/>
-        <v>773.07807879791994</v>
+        <v>747.15261878880005</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="3"/>
-        <v>788.53964037387823</v>
+        <v>762.09567116457606</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="3"/>
-        <v>804.31043318135585</v>
+        <v>777.33758458786747</v>
       </c>
       <c r="AO4" s="5">
         <f t="shared" si="3"/>
-        <v>820.39664184498292</v>
+        <v>785.11096043374619</v>
       </c>
       <c r="AP4" s="5">
         <f t="shared" ref="AP4:AS4" si="4">AP3-AP5</f>
-        <v>836.80457468188274</v>
+        <v>792.96207003808377</v>
       </c>
       <c r="AQ4" s="5">
         <f t="shared" si="4"/>
-        <v>853.5406661755203</v>
+        <v>800.89169073846438</v>
       </c>
       <c r="AR4" s="5">
         <f t="shared" si="4"/>
-        <v>870.61147949903102</v>
+        <v>808.90060764584905</v>
       </c>
       <c r="AS4" s="5">
         <f t="shared" si="4"/>
-        <v>888.02370908901162</v>
+        <v>816.98961372230769</v>
       </c>
     </row>
     <row r="5" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1272,7 +1275,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:V5" si="5">C3-C4</f>
+        <f t="shared" ref="C5:X5" si="5">C3-C4</f>
         <v>230.6</v>
       </c>
       <c r="D5" s="8">
@@ -1352,20 +1355,20 @@
         <v>236.59999999999994</v>
       </c>
       <c r="W5" s="8">
-        <f>W3*0.56</f>
-        <v>238.59023999999999</v>
+        <f t="shared" si="5"/>
+        <v>226.8</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" ref="X5:Z5" si="6">X3*0.56</f>
-        <v>248.80744000000001</v>
+        <f t="shared" si="5"/>
+        <v>238</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="6"/>
-        <v>243.95952000000005</v>
+        <f t="shared" ref="X5:Z5" si="6">Y3*0.56</f>
+        <v>236.78424000000004</v>
       </c>
       <c r="Z5" s="8">
         <f t="shared" si="6"/>
-        <v>239.96111999999994</v>
+        <v>237.60855999999995</v>
       </c>
       <c r="AB5" s="8">
         <f>AB3-AB4</f>
@@ -1384,7 +1387,7 @@
         <v>887.20000000000016</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" ref="AF5:AH5" si="7">AF3-AF4</f>
+        <f t="shared" ref="AF5:AI5" si="7">AF3-AF4</f>
         <v>882.19999999999982</v>
       </c>
       <c r="AG5" s="8">
@@ -1396,48 +1399,48 @@
         <v>989</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" ref="AI5" si="8">AI3*0.6</f>
-        <v>1040.6981999999998</v>
+        <f t="shared" si="7"/>
+        <v>939.19280000000003</v>
       </c>
       <c r="AJ5" s="8">
         <f>AJ3*0.57</f>
-        <v>1008.4365557999998</v>
+        <v>974.61826199999985</v>
       </c>
       <c r="AK5" s="8">
         <f>AK3*0.58</f>
-        <v>1046.6509937039998</v>
+        <v>1011.5511645599998</v>
       </c>
       <c r="AL5" s="8">
-        <f t="shared" ref="AL5:AS5" si="9">AL3*0.58</f>
-        <v>1067.5840135780797</v>
+        <f t="shared" ref="AL5:AS5" si="8">AL3*0.58</f>
+        <v>1031.7821878511998</v>
       </c>
       <c r="AM5" s="8">
-        <f t="shared" si="9"/>
-        <v>1088.9356938496414</v>
+        <f t="shared" si="8"/>
+        <v>1052.4178316082239</v>
       </c>
       <c r="AN5" s="8">
-        <f t="shared" si="9"/>
-        <v>1110.7144077266341</v>
+        <f t="shared" si="8"/>
+        <v>1073.4661882403884</v>
       </c>
       <c r="AO5" s="8">
-        <f t="shared" si="9"/>
-        <v>1132.928695881167</v>
+        <f t="shared" si="8"/>
+        <v>1084.2008501227922</v>
       </c>
       <c r="AP5" s="8">
-        <f t="shared" si="9"/>
-        <v>1155.5872697987902</v>
+        <f t="shared" si="8"/>
+        <v>1095.04285862402</v>
       </c>
       <c r="AQ5" s="8">
-        <f t="shared" si="9"/>
-        <v>1178.6990151947662</v>
+        <f t="shared" si="8"/>
+        <v>1105.9932872102604</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" si="9"/>
-        <v>1202.2729954986614</v>
+        <f t="shared" si="8"/>
+        <v>1117.0532200823629</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" si="9"/>
-        <v>1226.3184554086349</v>
+        <f t="shared" si="8"/>
+        <v>1128.2237522831865</v>
       </c>
     </row>
     <row r="6" spans="2:162" x14ac:dyDescent="0.3">
@@ -1506,20 +1509,18 @@
         <v>136.80000000000001</v>
       </c>
       <c r="W6" s="5">
-        <f>W3*0.34</f>
-        <v>144.85836</v>
+        <v>139.80000000000001</v>
       </c>
       <c r="X6" s="5">
-        <f t="shared" ref="X6:Z6" si="10">X3*0.34</f>
-        <v>151.06166000000002</v>
+        <v>143.80000000000001</v>
       </c>
       <c r="Y6" s="5">
-        <f t="shared" si="10"/>
-        <v>148.11828000000003</v>
+        <f t="shared" ref="X6:Z6" si="9">Y3*0.34</f>
+        <v>143.76186000000001</v>
       </c>
       <c r="Z6" s="5">
-        <f t="shared" si="10"/>
-        <v>145.69067999999996</v>
+        <f t="shared" si="9"/>
+        <v>144.26233999999997</v>
       </c>
       <c r="AB6" s="5">
         <v>342</v>
@@ -1562,31 +1563,31 @@
         <v>672.9383806080001</v>
       </c>
       <c r="AM6" s="5">
-        <f t="shared" ref="AM6:AO6" si="11">AL6*1.01</f>
+        <f t="shared" ref="AM6:AO6" si="10">AL6*1.01</f>
         <v>679.66776441408012</v>
       </c>
       <c r="AN6" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>686.46444205822092</v>
       </c>
       <c r="AO6" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>693.32908647880311</v>
       </c>
       <c r="AP6" s="5">
-        <f t="shared" ref="AP6" si="12">AO6*1.01</f>
+        <f t="shared" ref="AP6" si="11">AO6*1.01</f>
         <v>700.2623773435912</v>
       </c>
       <c r="AQ6" s="5">
-        <f t="shared" ref="AQ6" si="13">AP6*1.01</f>
+        <f t="shared" ref="AQ6" si="12">AP6*1.01</f>
         <v>707.26500111702717</v>
       </c>
       <c r="AR6" s="5">
-        <f t="shared" ref="AR6" si="14">AQ6*1.01</f>
+        <f t="shared" ref="AR6" si="13">AQ6*1.01</f>
         <v>714.33765112819742</v>
       </c>
       <c r="AS6" s="5">
-        <f t="shared" ref="AS6" si="15">AR6*1.01</f>
+        <f t="shared" ref="AS6" si="14">AR6*1.01</f>
         <v>721.48102763947941</v>
       </c>
     </row>
@@ -1655,10 +1656,18 @@
         <f>AH7-U7-T7-S7</f>
         <v>66.399999999999991</v>
       </c>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
+      <c r="W7" s="5">
+        <v>68.3</v>
+      </c>
+      <c r="X7" s="5">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>68</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>69</v>
+      </c>
       <c r="AB7" s="5">
         <v>234.3</v>
       </c>
@@ -1683,10 +1692,7 @@
       <c r="AH7" s="5">
         <v>273.39999999999998</v>
       </c>
-      <c r="AI7" s="5">
-        <f>AH7*0.98</f>
-        <v>267.93199999999996</v>
-      </c>
+      <c r="AI7" s="5"/>
       <c r="AJ7" s="5"/>
       <c r="AK7" s="5"/>
       <c r="AL7" s="5"/>
@@ -1763,10 +1769,18 @@
         <f>AH8-U8-T8-S8</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
+      <c r="W8" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="X8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <v>0</v>
+      </c>
       <c r="AB8" s="5">
         <v>0</v>
       </c>
@@ -1792,48 +1806,48 @@
         <v>0.8</v>
       </c>
       <c r="AI8" s="5">
-        <f t="shared" ref="AI8:AO8" si="16">AH8*0.9</f>
-        <v>0.72000000000000008</v>
+        <f>SUM(W8:Z8)</f>
+        <v>1.3</v>
       </c>
       <c r="AJ8" s="5">
-        <f t="shared" si="16"/>
-        <v>0.64800000000000013</v>
+        <f t="shared" ref="AJ8:AO8" si="15">AI8*0.9</f>
+        <v>1.1700000000000002</v>
       </c>
       <c r="AK8" s="5">
-        <f t="shared" si="16"/>
-        <v>0.58320000000000016</v>
+        <f t="shared" si="15"/>
+        <v>1.0530000000000002</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" si="16"/>
-        <v>0.52488000000000012</v>
+        <f t="shared" si="15"/>
+        <v>0.94770000000000021</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" si="16"/>
-        <v>0.47239200000000015</v>
+        <f t="shared" si="15"/>
+        <v>0.85293000000000019</v>
       </c>
       <c r="AN8" s="5">
-        <f t="shared" si="16"/>
-        <v>0.42515280000000016</v>
+        <f t="shared" si="15"/>
+        <v>0.76763700000000024</v>
       </c>
       <c r="AO8" s="5">
-        <f t="shared" si="16"/>
-        <v>0.38263752000000018</v>
+        <f t="shared" si="15"/>
+        <v>0.69087330000000025</v>
       </c>
       <c r="AP8" s="5">
-        <f t="shared" ref="AP8" si="17">AO8*0.9</f>
-        <v>0.34437376800000019</v>
+        <f t="shared" ref="AP8" si="16">AO8*0.9</f>
+        <v>0.62178597000000024</v>
       </c>
       <c r="AQ8" s="5">
-        <f t="shared" ref="AQ8" si="18">AP8*0.9</f>
-        <v>0.30993639120000016</v>
+        <f t="shared" ref="AQ8" si="17">AP8*0.9</f>
+        <v>0.55960737300000019</v>
       </c>
       <c r="AR8" s="5">
-        <f t="shared" ref="AR8" si="19">AQ8*0.9</f>
-        <v>0.27894275208000013</v>
+        <f t="shared" ref="AR8" si="18">AQ8*0.9</f>
+        <v>0.50364663570000023</v>
       </c>
       <c r="AS8" s="5">
-        <f t="shared" ref="AS8" si="20">AR8*0.9</f>
-        <v>0.2510484768720001</v>
+        <f t="shared" ref="AS8" si="19">AR8*0.9</f>
+        <v>0.45328197213000021</v>
       </c>
     </row>
     <row r="9" spans="2:162" x14ac:dyDescent="0.3">
@@ -1907,10 +1921,19 @@
         <f>AH9-U9-T9-S9</f>
         <v>3.8</v>
       </c>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
+      <c r="W9" s="5">
+        <f>7.8-0.6</f>
+        <v>7.2</v>
+      </c>
+      <c r="X9" s="5">
+        <v>5.9</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>2</v>
+      </c>
       <c r="AB9" s="5">
         <v>57.8</v>
       </c>
@@ -1939,7 +1962,8 @@
         <v>6</v>
       </c>
       <c r="AI9" s="5">
-        <v>0</v>
+        <f>SUM(W9:Z9)</f>
+        <v>18.100000000000001</v>
       </c>
       <c r="AJ9" s="5">
         <v>0</v>
@@ -1977,89 +2001,101 @@
         <v>26</v>
       </c>
       <c r="C10" s="8">
-        <f t="shared" ref="C10:D10" si="21">C5-C6-C7-C8-C9</f>
+        <f t="shared" ref="C10:D10" si="20">C5-C6-C7-C8-C9</f>
         <v>-15.800000000000004</v>
       </c>
       <c r="D10" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>33.500000000000007</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" ref="E10" si="22">E5-E6-E7-E8-E9</f>
+        <f t="shared" ref="E10" si="21">E5-E6-E7-E8-E9</f>
         <v>-3.9999999999999987</v>
       </c>
       <c r="F10" s="8">
-        <f t="shared" ref="F10" si="23">F5-F6-F7-F8-F9</f>
+        <f t="shared" ref="F10" si="22">F5-F6-F7-F8-F9</f>
         <v>27.200000000000003</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" ref="G10:H10" si="24">G5-G6-G7-G8-G9</f>
+        <f t="shared" ref="G10:H10" si="23">G5-G6-G7-G8-G9</f>
         <v>-36.700000000000024</v>
       </c>
       <c r="H10" s="8">
+        <f t="shared" si="23"/>
+        <v>39.500000000000007</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" ref="I10:J10" si="24">I5-I6-I7-I8-I9</f>
+        <v>-301.09999999999997</v>
+      </c>
+      <c r="J10" s="8">
         <f t="shared" si="24"/>
-        <v>39.500000000000007</v>
-      </c>
-      <c r="I10" s="8">
-        <f t="shared" ref="I10:J10" si="25">I5-I6-I7-I8-I9</f>
-        <v>-301.09999999999997</v>
-      </c>
-      <c r="J10" s="8">
+        <v>28.999999999999993</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" ref="K10:L10" si="25">K5-K6-K7-K8-K9</f>
+        <v>-1191.7</v>
+      </c>
+      <c r="L10" s="8">
         <f t="shared" si="25"/>
-        <v>28.999999999999993</v>
-      </c>
-      <c r="K10" s="8">
-        <f t="shared" ref="K10:L10" si="26">K5-K6-K7-K8-K9</f>
-        <v>-1191.7</v>
-      </c>
-      <c r="L10" s="8">
-        <f t="shared" si="26"/>
         <v>-703.19999999999993</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" ref="M10" si="27">M5-M6-M7-M8-M9</f>
+        <f t="shared" ref="M10" si="26">M5-M6-M7-M8-M9</f>
         <v>4.6999999999999824</v>
       </c>
       <c r="N10" s="8">
-        <f t="shared" ref="N10" si="28">N5-N6-N7-N8-N9</f>
+        <f t="shared" ref="N10" si="27">N5-N6-N7-N8-N9</f>
         <v>18.300000000000026</v>
       </c>
       <c r="O10" s="8">
-        <f t="shared" ref="O10:P10" si="29">O5-O6-O7-O8-O9</f>
+        <f t="shared" ref="O10:P10" si="28">O5-O6-O7-O8-O9</f>
         <v>34.899999999999991</v>
       </c>
       <c r="P10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>34.200000000000017</v>
       </c>
       <c r="Q10" s="8">
-        <f t="shared" ref="Q10" si="30">Q5-Q6-Q7-Q8-Q9</f>
+        <f t="shared" ref="Q10" si="29">Q5-Q6-Q7-Q8-Q9</f>
         <v>43.199999999999989</v>
       </c>
       <c r="R10" s="8">
-        <f t="shared" ref="R10" si="31">R5-R6-R7-R8-R9</f>
+        <f t="shared" ref="R10" si="30">R5-R6-R7-R8-R9</f>
         <v>46.2</v>
       </c>
       <c r="S10" s="8">
-        <f t="shared" ref="S10:V10" si="32">S5-S6-S7-S8-S9</f>
+        <f t="shared" ref="S10:V10" si="31">S5-S6-S7-S8-S9</f>
         <v>32.799999999999969</v>
       </c>
       <c r="T10" s="8">
+        <f t="shared" si="31"/>
+        <v>36.499999999999979</v>
+      </c>
+      <c r="U10" s="8">
+        <f t="shared" si="31"/>
+        <v>34.400000000000027</v>
+      </c>
+      <c r="V10" s="8">
+        <f t="shared" si="31"/>
+        <v>29.499999999999932</v>
+      </c>
+      <c r="W10" s="8">
+        <f t="shared" ref="W10:Z10" si="32">W5-W6-W7-W8-W9</f>
+        <v>10.200000000000003</v>
+      </c>
+      <c r="X10" s="8">
         <f t="shared" si="32"/>
-        <v>36.499999999999979</v>
-      </c>
-      <c r="U10" s="8">
+        <v>20.699999999999996</v>
+      </c>
+      <c r="Y10" s="8">
         <f t="shared" si="32"/>
-        <v>34.400000000000027</v>
-      </c>
-      <c r="V10" s="8">
+        <v>22.022380000000027</v>
+      </c>
+      <c r="Z10" s="8">
         <f t="shared" si="32"/>
-        <v>29.499999999999932</v>
-      </c>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
+        <v>22.346219999999988</v>
+      </c>
       <c r="AB10" s="8">
         <f>AB5-AB6-AB7-AB8-AB9</f>
         <v>115.89999999999999</v>
@@ -2090,47 +2126,47 @@
       </c>
       <c r="AI10" s="8">
         <f t="shared" si="33"/>
-        <v>156.1541999999998</v>
+        <v>303.90079999999995</v>
       </c>
       <c r="AJ10" s="8">
         <f t="shared" si="33"/>
-        <v>367.26087579999978</v>
+        <v>332.9205819999998</v>
       </c>
       <c r="AK10" s="8">
         <f t="shared" si="33"/>
-        <v>386.32428330399972</v>
+        <v>350.75465415999975</v>
       </c>
       <c r="AL10" s="8">
         <f t="shared" si="33"/>
-        <v>394.12075297007965</v>
+        <v>357.89610724319965</v>
       </c>
       <c r="AM10" s="8">
         <f t="shared" si="33"/>
-        <v>408.7955374355613</v>
+        <v>371.89713719414374</v>
       </c>
       <c r="AN10" s="8">
         <f t="shared" si="33"/>
-        <v>423.82481286841323</v>
+        <v>386.23410918216751</v>
       </c>
       <c r="AO10" s="8">
         <f t="shared" si="33"/>
-        <v>439.21697188236385</v>
+        <v>390.18089034398906</v>
       </c>
       <c r="AP10" s="8">
         <f t="shared" ref="AP10:AS10" si="34">AP5-AP6-AP7-AP8-AP9</f>
-        <v>454.98051868719898</v>
+        <v>394.15869531042881</v>
       </c>
       <c r="AQ10" s="8">
         <f t="shared" si="34"/>
-        <v>471.12407768653901</v>
+        <v>398.16867872023323</v>
       </c>
       <c r="AR10" s="8">
         <f t="shared" si="34"/>
-        <v>487.656401618384</v>
+        <v>402.2119223184655</v>
       </c>
       <c r="AS10" s="8">
         <f t="shared" si="34"/>
-        <v>504.58637929228354</v>
+        <v>406.28944267157709</v>
       </c>
     </row>
     <row r="11" spans="2:162" x14ac:dyDescent="0.3">
@@ -2198,10 +2234,18 @@
         <f>AH11-U11-T11-S11</f>
         <v>-19.400000000000006</v>
       </c>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
+      <c r="W11" s="5">
+        <v>-0.8</v>
+      </c>
+      <c r="X11" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>0</v>
+      </c>
       <c r="AB11" s="5">
         <v>-6</v>
       </c>
@@ -2227,48 +2271,48 @@
         <v>-21.5</v>
       </c>
       <c r="AI11" s="5">
-        <f>AH11*1.05</f>
-        <v>-22.574999999999999</v>
+        <f>SUM(W11:Z11)</f>
+        <v>5.9</v>
       </c>
       <c r="AJ11" s="5">
         <f t="shared" ref="AJ11:AS11" si="35">AI11*1.05</f>
-        <v>-23.703749999999999</v>
+        <v>6.1950000000000003</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="35"/>
-        <v>-24.888937500000001</v>
+        <v>6.5047500000000005</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="35"/>
-        <v>-26.133384375000002</v>
+        <v>6.8299875000000005</v>
       </c>
       <c r="AM11" s="5">
         <f t="shared" si="35"/>
-        <v>-27.440053593750005</v>
+        <v>7.1714868750000011</v>
       </c>
       <c r="AN11" s="5">
         <f t="shared" si="35"/>
-        <v>-28.812056273437506</v>
+        <v>7.5300612187500011</v>
       </c>
       <c r="AO11" s="5">
         <f t="shared" si="35"/>
-        <v>-30.252659087109382</v>
+        <v>7.9065642796875011</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" si="35"/>
-        <v>-31.765292041464853</v>
+        <v>8.3018924936718772</v>
       </c>
       <c r="AQ11" s="5">
         <f t="shared" si="35"/>
-        <v>-33.353556643538099</v>
+        <v>8.7169871183554708</v>
       </c>
       <c r="AR11" s="5">
         <f t="shared" si="35"/>
-        <v>-35.021234475715005</v>
+        <v>9.1528364742732453</v>
       </c>
       <c r="AS11" s="5">
         <f t="shared" si="35"/>
-        <v>-36.772296199500758</v>
+        <v>9.6104782979869086</v>
       </c>
     </row>
     <row r="12" spans="2:162" x14ac:dyDescent="0.3">
@@ -2336,10 +2380,18 @@
         <f>AH12-U12-T12-S12</f>
         <v>33.200000000000017</v>
       </c>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
+      <c r="W12" s="5">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="X12" s="5">
+        <v>34.5</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>33</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>33</v>
+      </c>
       <c r="AB12" s="5">
         <v>156</v>
       </c>
@@ -2365,48 +2417,48 @@
         <v>140.80000000000001</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" ref="AI12:AO12" si="36">AH12*0.8</f>
-        <v>112.64000000000001</v>
+        <f>SUM(W12:Z12)</f>
+        <v>134.19999999999999</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="36"/>
-        <v>90.112000000000023</v>
+        <f t="shared" ref="AJ12:AO12" si="36">AI12*0.8</f>
+        <v>107.36</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="36"/>
-        <v>72.089600000000019</v>
+        <v>85.888000000000005</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="36"/>
-        <v>57.671680000000016</v>
+        <v>68.710400000000007</v>
       </c>
       <c r="AM12" s="5">
         <f t="shared" si="36"/>
-        <v>46.137344000000013</v>
+        <v>54.968320000000006</v>
       </c>
       <c r="AN12" s="5">
         <f t="shared" si="36"/>
-        <v>36.909875200000009</v>
+        <v>43.97465600000001</v>
       </c>
       <c r="AO12" s="5">
         <f t="shared" si="36"/>
-        <v>29.527900160000009</v>
+        <v>35.17972480000001</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" ref="AP12" si="37">AO12*0.8</f>
-        <v>23.622320128000009</v>
+        <v>28.143779840000008</v>
       </c>
       <c r="AQ12" s="5">
         <f t="shared" ref="AQ12" si="38">AP12*0.8</f>
-        <v>18.897856102400009</v>
+        <v>22.515023872000008</v>
       </c>
       <c r="AR12" s="5">
         <f t="shared" ref="AR12" si="39">AQ12*0.8</f>
-        <v>15.118284881920008</v>
+        <v>18.012019097600007</v>
       </c>
       <c r="AS12" s="5">
         <f t="shared" ref="AS12" si="40">AR12*0.8</f>
-        <v>12.094627905536008</v>
+        <v>14.409615278080006</v>
       </c>
     </row>
     <row r="13" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2493,10 +2545,22 @@
         <f t="shared" si="52"/>
         <v>15.699999999999918</v>
       </c>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
+      <c r="W13" s="8">
+        <f t="shared" ref="W13:Z13" si="53">W10-W11-W12</f>
+        <v>-22.7</v>
+      </c>
+      <c r="X13" s="8">
+        <f t="shared" si="53"/>
+        <v>-20.500000000000004</v>
+      </c>
+      <c r="Y13" s="8">
+        <f t="shared" si="53"/>
+        <v>-10.977619999999973</v>
+      </c>
+      <c r="Z13" s="8">
+        <f t="shared" si="53"/>
+        <v>-10.653780000000012</v>
+      </c>
       <c r="AB13" s="8">
         <f>AB10-AB11-AB12</f>
         <v>-34.100000000000009</v>
@@ -2514,60 +2578,60 @@
         <v>-195.49999999999986</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" ref="AF13:AO13" si="53">AF10-AF11-AF12</f>
+        <f t="shared" ref="AF13:AO13" si="54">AF10-AF11-AF12</f>
         <v>-1914.7</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>20.499999999999972</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>13.899999999999977</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="53"/>
-        <v>66.089199999999778</v>
+        <f t="shared" si="54"/>
+        <v>163.80079999999998</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="53"/>
-        <v>300.85262579999977</v>
+        <f t="shared" si="54"/>
+        <v>219.36558199999979</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="53"/>
-        <v>339.1236208039997</v>
+        <f t="shared" si="54"/>
+        <v>258.36190415999977</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" si="53"/>
-        <v>362.5824573450796</v>
+        <f t="shared" si="54"/>
+        <v>282.35571974319964</v>
       </c>
       <c r="AM13" s="8">
-        <f t="shared" si="53"/>
-        <v>390.09824702931132</v>
+        <f t="shared" si="54"/>
+        <v>309.7573303191437</v>
       </c>
       <c r="AN13" s="8">
-        <f t="shared" si="53"/>
-        <v>415.72699394185076</v>
+        <f t="shared" si="54"/>
+        <v>334.72939196341747</v>
       </c>
       <c r="AO13" s="8">
-        <f t="shared" si="53"/>
-        <v>439.94173080947326</v>
+        <f t="shared" si="54"/>
+        <v>347.09460126430156</v>
       </c>
       <c r="AP13" s="8">
-        <f t="shared" ref="AP13:AS13" si="54">AP10-AP11-AP12</f>
-        <v>463.12349060066384</v>
+        <f t="shared" ref="AP13:AS13" si="55">AP10-AP11-AP12</f>
+        <v>357.71302297675697</v>
       </c>
       <c r="AQ13" s="8">
-        <f t="shared" si="54"/>
-        <v>485.57977822767708</v>
+        <f t="shared" si="55"/>
+        <v>366.93666772987774</v>
       </c>
       <c r="AR13" s="8">
-        <f t="shared" si="54"/>
-        <v>507.55935121217891</v>
+        <f t="shared" si="55"/>
+        <v>375.04706674659224</v>
       </c>
       <c r="AS13" s="8">
-        <f t="shared" si="54"/>
-        <v>529.26404758624835</v>
+        <f t="shared" si="55"/>
+        <v>382.26934909551017</v>
       </c>
     </row>
     <row r="14" spans="2:162" x14ac:dyDescent="0.3">
@@ -2635,10 +2699,20 @@
         <f>AH14-U14-T14-S14</f>
         <v>-17.7</v>
       </c>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="5"/>
+      <c r="W14" s="5">
+        <v>-3.1</v>
+      </c>
+      <c r="X14" s="5">
+        <v>29.4</v>
+      </c>
+      <c r="Y14" s="5">
+        <f t="shared" ref="Y14:Z14" si="56">Y13*0.05</f>
+        <v>-0.54888099999999873</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" si="56"/>
+        <v>-0.53268900000000063</v>
+      </c>
       <c r="AB14" s="5">
         <v>5.6</v>
       </c>
@@ -2664,48 +2738,48 @@
         <v>-8.1</v>
       </c>
       <c r="AI14" s="5">
-        <f>AI13*0.25</f>
-        <v>16.522299999999944</v>
+        <f>SUM(W14:Z14)</f>
+        <v>25.218429999999998</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" ref="AJ14:AS14" si="55">AJ13*0.25</f>
-        <v>75.213156449999943</v>
+        <f>AJ13*0.2</f>
+        <v>43.873116399999958</v>
       </c>
       <c r="AK14" s="5">
-        <f t="shared" si="55"/>
-        <v>84.780905200999925</v>
+        <f t="shared" ref="AK14:AS14" si="57">AK13*0.2</f>
+        <v>51.672380831999959</v>
       </c>
       <c r="AL14" s="5">
-        <f t="shared" si="55"/>
-        <v>90.645614336269901</v>
+        <f t="shared" si="57"/>
+        <v>56.471143948639934</v>
       </c>
       <c r="AM14" s="5">
-        <f t="shared" si="55"/>
-        <v>97.524561757327831</v>
+        <f t="shared" si="57"/>
+        <v>61.951466063828747</v>
       </c>
       <c r="AN14" s="5">
-        <f t="shared" si="55"/>
-        <v>103.93174848546269</v>
+        <f t="shared" si="57"/>
+        <v>66.945878392683497</v>
       </c>
       <c r="AO14" s="5">
-        <f t="shared" si="55"/>
-        <v>109.98543270236831</v>
+        <f t="shared" si="57"/>
+        <v>69.418920252860318</v>
       </c>
       <c r="AP14" s="5">
-        <f t="shared" si="55"/>
-        <v>115.78087265016596</v>
+        <f t="shared" si="57"/>
+        <v>71.542604595351392</v>
       </c>
       <c r="AQ14" s="5">
-        <f t="shared" si="55"/>
-        <v>121.39494455691927</v>
+        <f t="shared" si="57"/>
+        <v>73.387333545975551</v>
       </c>
       <c r="AR14" s="5">
-        <f t="shared" si="55"/>
-        <v>126.88983780304473</v>
+        <f t="shared" si="57"/>
+        <v>75.00941334931845</v>
       </c>
       <c r="AS14" s="5">
-        <f t="shared" si="55"/>
-        <v>132.31601189656209</v>
+        <f t="shared" si="57"/>
+        <v>76.453869819102039</v>
       </c>
     </row>
     <row r="15" spans="2:162" x14ac:dyDescent="0.3">
@@ -2773,10 +2847,18 @@
         <f>AH15-U15-T15-S15</f>
         <v>0</v>
       </c>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
+      <c r="X15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <v>0</v>
+      </c>
       <c r="AB15" s="5">
         <v>0</v>
       </c>
@@ -2802,6 +2884,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="5">
+        <f>SUM(W15:Z15)</f>
         <v>0</v>
       </c>
       <c r="AJ15" s="5">
@@ -2840,89 +2923,101 @@
         <v>32</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:D16" si="56">C13-C14-C15</f>
+        <f t="shared" ref="C16:D16" si="58">C13-C14-C15</f>
         <v>-51.20000000000001</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>-15.899999999999993</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" ref="E16" si="57">E13-E14-E15</f>
+        <f t="shared" ref="E16" si="59">E13-E14-E15</f>
         <v>-38.299999999999997</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" ref="F16" si="58">F13-F14-F15</f>
+        <f t="shared" ref="F16" si="60">F13-F14-F15</f>
         <v>-3.2999999999999949</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" ref="G16:H16" si="59">G13-G14-G15</f>
+        <f t="shared" ref="G16:H16" si="61">G13-G14-G15</f>
         <v>-60.800000000000026</v>
       </c>
       <c r="H16" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>6.5000000000000062</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" ref="I16:J16" si="60">I13-I14-I15</f>
+        <f t="shared" ref="I16:J16" si="62">I13-I14-I15</f>
         <v>-147.09999999999997</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>90.399999999999991</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" ref="K16:L16" si="61">K13-K14-K15</f>
+        <f t="shared" ref="K16:L16" si="63">K13-K14-K15</f>
         <v>-1171.2</v>
       </c>
       <c r="L16" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-691.99999999999989</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" ref="M16" si="62">M13-M14-M15</f>
+        <f t="shared" ref="M16" si="64">M13-M14-M15</f>
         <v>0.99999999999998312</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" ref="N16" si="63">N13-N14-N15</f>
+        <f t="shared" ref="N16" si="65">N13-N14-N15</f>
         <v>-33.199999999999974</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" ref="O16:P16" si="64">O13-O14-O15</f>
+        <f t="shared" ref="O16:P16" si="66">O13-O14-O15</f>
         <v>-3.9</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-1.7999999999999812</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" ref="Q16" si="65">Q13-Q14-Q15</f>
+        <f t="shared" ref="Q16" si="67">Q13-Q14-Q15</f>
         <v>-2.5000000000000071</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" ref="R16" si="66">R13-R14-R15</f>
+        <f t="shared" ref="R16" si="68">R13-R14-R15</f>
         <v>-12.199999999999998</v>
       </c>
       <c r="S16" s="8">
-        <f t="shared" ref="S16:V16" si="67">S13-S14-S15</f>
+        <f t="shared" ref="S16:V16" si="69">S13-S14-S15</f>
         <v>2.8999999999999675</v>
       </c>
       <c r="T16" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>-1.4000000000000243</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>-12.899999999999972</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>33.39999999999992</v>
       </c>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
+      <c r="W16" s="8">
+        <f t="shared" ref="W16:Z16" si="70">W13-W14-W15</f>
+        <v>-19.599999999999998</v>
+      </c>
+      <c r="X16" s="8">
+        <f t="shared" si="70"/>
+        <v>-49.900000000000006</v>
+      </c>
+      <c r="Y16" s="8">
+        <f t="shared" si="70"/>
+        <v>-10.428738999999975</v>
+      </c>
+      <c r="Z16" s="8">
+        <f t="shared" si="70"/>
+        <v>-10.12109100000001</v>
+      </c>
       <c r="AB16" s="8">
         <f>AB13-AB14-AB15</f>
         <v>-39.70000000000001</v>
@@ -2944,527 +3039,527 @@
         <v>-1895.4</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" ref="AG16:AO16" si="68">AG13-AG14-AG15</f>
+        <f t="shared" ref="AG16:AO16" si="71">AG13-AG14-AG15</f>
         <v>-20.400000000000027</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>21.999999999999979</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="68"/>
-        <v>49.566899999999833</v>
+        <f t="shared" si="71"/>
+        <v>138.58236999999997</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="68"/>
-        <v>225.63946934999984</v>
+        <f t="shared" si="71"/>
+        <v>175.49246559999983</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="68"/>
-        <v>254.34271560299976</v>
+        <f t="shared" si="71"/>
+        <v>206.68952332799981</v>
       </c>
       <c r="AL16" s="8">
-        <f t="shared" si="68"/>
-        <v>271.93684300880972</v>
+        <f t="shared" si="71"/>
+        <v>225.88457579455971</v>
       </c>
       <c r="AM16" s="8">
-        <f t="shared" si="68"/>
-        <v>292.57368527198349</v>
+        <f t="shared" si="71"/>
+        <v>247.80586425531496</v>
       </c>
       <c r="AN16" s="8">
-        <f t="shared" si="68"/>
-        <v>311.7952454563881</v>
+        <f t="shared" si="71"/>
+        <v>267.78351357073399</v>
       </c>
       <c r="AO16" s="8">
-        <f t="shared" si="68"/>
-        <v>329.95629810710494</v>
+        <f t="shared" si="71"/>
+        <v>277.67568101144127</v>
       </c>
       <c r="AP16" s="8">
-        <f t="shared" ref="AP16:AS16" si="69">AP13-AP14-AP15</f>
-        <v>347.34261795049787</v>
+        <f t="shared" ref="AP16:AS16" si="72">AP13-AP14-AP15</f>
+        <v>286.17041838140557</v>
       </c>
       <c r="AQ16" s="8">
-        <f t="shared" si="69"/>
-        <v>364.18483367075783</v>
+        <f t="shared" si="72"/>
+        <v>293.5493341839022</v>
       </c>
       <c r="AR16" s="8">
-        <f t="shared" si="69"/>
-        <v>380.6695134091342</v>
+        <f t="shared" si="72"/>
+        <v>300.0376533972738</v>
       </c>
       <c r="AS16" s="8">
-        <f t="shared" si="69"/>
-        <v>396.94803568968626</v>
+        <f t="shared" si="72"/>
+        <v>305.81547927640815</v>
       </c>
       <c r="AT16" s="1">
         <f>AS16*(1+$AV$21)</f>
-        <v>392.97855533278943</v>
+        <v>302.75732448364408</v>
       </c>
       <c r="AU16" s="1">
-        <f t="shared" ref="AU16:DF16" si="70">AT16*(1+$AV$21)</f>
-        <v>389.04876977946151</v>
+        <f t="shared" ref="AU16:DF16" si="73">AT16*(1+$AV$21)</f>
+        <v>299.72975123880764</v>
       </c>
       <c r="AV16" s="1">
-        <f t="shared" si="70"/>
-        <v>385.15828208166687</v>
+        <f t="shared" si="73"/>
+        <v>296.73245372641958</v>
       </c>
       <c r="AW16" s="1">
-        <f t="shared" si="70"/>
-        <v>381.30669926085022</v>
+        <f t="shared" si="73"/>
+        <v>293.7651291891554</v>
       </c>
       <c r="AX16" s="1">
-        <f t="shared" si="70"/>
-        <v>377.4936322682417</v>
+        <f t="shared" si="73"/>
+        <v>290.82747789726386</v>
       </c>
       <c r="AY16" s="1">
-        <f t="shared" si="70"/>
-        <v>373.71869594555926</v>
+        <f t="shared" si="73"/>
+        <v>287.91920311829119</v>
       </c>
       <c r="AZ16" s="1">
-        <f t="shared" si="70"/>
-        <v>369.98150898610368</v>
+        <f t="shared" si="73"/>
+        <v>285.04001108710827</v>
       </c>
       <c r="BA16" s="1">
-        <f t="shared" si="70"/>
-        <v>366.28169389624264</v>
+        <f t="shared" si="73"/>
+        <v>282.18961097623719</v>
       </c>
       <c r="BB16" s="1">
-        <f t="shared" si="70"/>
-        <v>362.61887695728024</v>
+        <f t="shared" si="73"/>
+        <v>279.36771486647484</v>
       </c>
       <c r="BC16" s="1">
-        <f t="shared" si="70"/>
-        <v>358.99268818770742</v>
+        <f t="shared" si="73"/>
+        <v>276.57403771781009</v>
       </c>
       <c r="BD16" s="1">
-        <f t="shared" si="70"/>
-        <v>355.40276130583032</v>
+        <f t="shared" si="73"/>
+        <v>273.80829734063201</v>
       </c>
       <c r="BE16" s="1">
-        <f t="shared" si="70"/>
-        <v>351.84873369277204</v>
+        <f t="shared" si="73"/>
+        <v>271.07021436722567</v>
       </c>
       <c r="BF16" s="1">
-        <f t="shared" si="70"/>
-        <v>348.33024635584434</v>
+        <f t="shared" si="73"/>
+        <v>268.35951222355339</v>
       </c>
       <c r="BG16" s="1">
-        <f t="shared" si="70"/>
-        <v>344.84694389228588</v>
+        <f t="shared" si="73"/>
+        <v>265.67591710131785</v>
       </c>
       <c r="BH16" s="1">
-        <f t="shared" si="70"/>
-        <v>341.39847445336301</v>
+        <f t="shared" si="73"/>
+        <v>263.01915793030469</v>
       </c>
       <c r="BI16" s="1">
-        <f t="shared" si="70"/>
-        <v>337.98448970882936</v>
+        <f t="shared" si="73"/>
+        <v>260.38896635100161</v>
       </c>
       <c r="BJ16" s="1">
-        <f t="shared" si="70"/>
-        <v>334.60464481174108</v>
+        <f t="shared" si="73"/>
+        <v>257.7850766874916</v>
       </c>
       <c r="BK16" s="1">
-        <f t="shared" si="70"/>
-        <v>331.25859836362366</v>
+        <f t="shared" si="73"/>
+        <v>255.20722592061668</v>
       </c>
       <c r="BL16" s="1">
-        <f t="shared" si="70"/>
-        <v>327.94601237998739</v>
+        <f t="shared" si="73"/>
+        <v>252.65515366141051</v>
       </c>
       <c r="BM16" s="1">
-        <f t="shared" si="70"/>
-        <v>324.66655225618752</v>
+        <f t="shared" si="73"/>
+        <v>250.1286021247964</v>
       </c>
       <c r="BN16" s="1">
-        <f t="shared" si="70"/>
-        <v>321.41988673362562</v>
+        <f t="shared" si="73"/>
+        <v>247.62731610354842</v>
       </c>
       <c r="BO16" s="1">
-        <f t="shared" si="70"/>
-        <v>318.20568786628934</v>
+        <f t="shared" si="73"/>
+        <v>245.15104294251293</v>
       </c>
       <c r="BP16" s="1">
-        <f t="shared" si="70"/>
-        <v>315.02363098762646</v>
+        <f t="shared" si="73"/>
+        <v>242.6995325130878</v>
       </c>
       <c r="BQ16" s="1">
-        <f t="shared" si="70"/>
-        <v>311.87339467775018</v>
+        <f t="shared" si="73"/>
+        <v>240.27253718795691</v>
       </c>
       <c r="BR16" s="1">
-        <f t="shared" si="70"/>
-        <v>308.75466073097266</v>
+        <f t="shared" si="73"/>
+        <v>237.86981181607734</v>
       </c>
       <c r="BS16" s="1">
-        <f t="shared" si="70"/>
-        <v>305.66711412366294</v>
+        <f t="shared" si="73"/>
+        <v>235.49111369791657</v>
       </c>
       <c r="BT16" s="1">
-        <f t="shared" si="70"/>
-        <v>302.61044298242632</v>
+        <f t="shared" si="73"/>
+        <v>233.13620256093742</v>
       </c>
       <c r="BU16" s="1">
-        <f t="shared" si="70"/>
-        <v>299.58433855260205</v>
+        <f t="shared" si="73"/>
+        <v>230.80484053532805</v>
       </c>
       <c r="BV16" s="1">
-        <f t="shared" si="70"/>
-        <v>296.58849516707602</v>
+        <f t="shared" si="73"/>
+        <v>228.49679212997478</v>
       </c>
       <c r="BW16" s="1">
-        <f t="shared" si="70"/>
-        <v>293.62261021540525</v>
+        <f t="shared" si="73"/>
+        <v>226.21182420867504</v>
       </c>
       <c r="BX16" s="1">
-        <f t="shared" si="70"/>
-        <v>290.68638411325117</v>
+        <f t="shared" si="73"/>
+        <v>223.94970596658828</v>
       </c>
       <c r="BY16" s="1">
-        <f t="shared" si="70"/>
-        <v>287.77952027211865</v>
+        <f t="shared" si="73"/>
+        <v>221.71020890692239</v>
       </c>
       <c r="BZ16" s="1">
-        <f t="shared" si="70"/>
-        <v>284.90172506939746</v>
+        <f t="shared" si="73"/>
+        <v>219.49310681785317</v>
       </c>
       <c r="CA16" s="1">
-        <f t="shared" si="70"/>
-        <v>282.05270781870348</v>
+        <f t="shared" si="73"/>
+        <v>217.29817574967464</v>
       </c>
       <c r="CB16" s="1">
-        <f t="shared" si="70"/>
-        <v>279.23218074051647</v>
+        <f t="shared" si="73"/>
+        <v>215.12519399217788</v>
       </c>
       <c r="CC16" s="1">
-        <f t="shared" si="70"/>
-        <v>276.43985893311128</v>
+        <f t="shared" si="73"/>
+        <v>212.97394205225609</v>
       </c>
       <c r="CD16" s="1">
-        <f t="shared" si="70"/>
-        <v>273.67546034378017</v>
+        <f t="shared" si="73"/>
+        <v>210.84420263173354</v>
       </c>
       <c r="CE16" s="1">
-        <f t="shared" si="70"/>
-        <v>270.93870574034236</v>
+        <f t="shared" si="73"/>
+        <v>208.7357606054162</v>
       </c>
       <c r="CF16" s="1">
-        <f t="shared" si="70"/>
-        <v>268.22931868293892</v>
+        <f t="shared" si="73"/>
+        <v>206.64840299936205</v>
       </c>
       <c r="CG16" s="1">
-        <f t="shared" si="70"/>
-        <v>265.54702549610954</v>
+        <f t="shared" si="73"/>
+        <v>204.58191896936842</v>
       </c>
       <c r="CH16" s="1">
-        <f t="shared" si="70"/>
-        <v>262.89155524114847</v>
+        <f t="shared" si="73"/>
+        <v>202.53609977967474</v>
       </c>
       <c r="CI16" s="1">
-        <f t="shared" si="70"/>
-        <v>260.26263968873695</v>
+        <f t="shared" si="73"/>
+        <v>200.51073878187799</v>
       </c>
       <c r="CJ16" s="1">
-        <f t="shared" si="70"/>
-        <v>257.66001329184957</v>
+        <f t="shared" si="73"/>
+        <v>198.50563139405921</v>
       </c>
       <c r="CK16" s="1">
-        <f t="shared" si="70"/>
-        <v>255.08341315893108</v>
+        <f t="shared" si="73"/>
+        <v>196.52057508011862</v>
       </c>
       <c r="CL16" s="1">
-        <f t="shared" si="70"/>
-        <v>252.53257902734177</v>
+        <f t="shared" si="73"/>
+        <v>194.55536932931744</v>
       </c>
       <c r="CM16" s="1">
-        <f t="shared" si="70"/>
-        <v>250.00725323706834</v>
+        <f t="shared" si="73"/>
+        <v>192.60981563602428</v>
       </c>
       <c r="CN16" s="1">
-        <f t="shared" si="70"/>
-        <v>247.50718070469765</v>
+        <f t="shared" si="73"/>
+        <v>190.68371747966404</v>
       </c>
       <c r="CO16" s="1">
-        <f t="shared" si="70"/>
-        <v>245.03210889765066</v>
+        <f t="shared" si="73"/>
+        <v>188.7768803048674</v>
       </c>
       <c r="CP16" s="1">
-        <f t="shared" si="70"/>
-        <v>242.58178780867414</v>
+        <f t="shared" si="73"/>
+        <v>186.88911150181872</v>
       </c>
       <c r="CQ16" s="1">
-        <f t="shared" si="70"/>
-        <v>240.15596993058739</v>
+        <f t="shared" si="73"/>
+        <v>185.02022038680053</v>
       </c>
       <c r="CR16" s="1">
-        <f t="shared" si="70"/>
-        <v>237.75441023128153</v>
+        <f t="shared" si="73"/>
+        <v>183.17001818293252</v>
       </c>
       <c r="CS16" s="1">
-        <f t="shared" si="70"/>
-        <v>235.37686612896871</v>
+        <f t="shared" si="73"/>
+        <v>181.3383180011032</v>
       </c>
       <c r="CT16" s="1">
-        <f t="shared" si="70"/>
-        <v>233.02309746767904</v>
+        <f t="shared" si="73"/>
+        <v>179.52493482109216</v>
       </c>
       <c r="CU16" s="1">
-        <f t="shared" si="70"/>
-        <v>230.69286649300224</v>
+        <f t="shared" si="73"/>
+        <v>177.72968547288124</v>
       </c>
       <c r="CV16" s="1">
-        <f t="shared" si="70"/>
-        <v>228.38593782807223</v>
+        <f t="shared" si="73"/>
+        <v>175.95238861815244</v>
       </c>
       <c r="CW16" s="1">
-        <f t="shared" si="70"/>
-        <v>226.10207844979149</v>
+        <f t="shared" si="73"/>
+        <v>174.19286473197093</v>
       </c>
       <c r="CX16" s="1">
-        <f t="shared" si="70"/>
-        <v>223.84105766529356</v>
+        <f t="shared" si="73"/>
+        <v>172.4509360846512</v>
       </c>
       <c r="CY16" s="1">
-        <f t="shared" si="70"/>
-        <v>221.60264708864062</v>
+        <f t="shared" si="73"/>
+        <v>170.72642672380468</v>
       </c>
       <c r="CZ16" s="1">
-        <f t="shared" si="70"/>
-        <v>219.3866206177542</v>
+        <f t="shared" si="73"/>
+        <v>169.01916245656662</v>
       </c>
       <c r="DA16" s="1">
-        <f t="shared" si="70"/>
-        <v>217.19275441157666</v>
+        <f t="shared" si="73"/>
+        <v>167.32897083200095</v>
       </c>
       <c r="DB16" s="1">
-        <f t="shared" si="70"/>
-        <v>215.0208268674609</v>
+        <f t="shared" si="73"/>
+        <v>165.65568112368095</v>
       </c>
       <c r="DC16" s="1">
-        <f t="shared" si="70"/>
-        <v>212.87061859878628</v>
+        <f t="shared" si="73"/>
+        <v>163.99912431244414</v>
       </c>
       <c r="DD16" s="1">
-        <f t="shared" si="70"/>
-        <v>210.74191241279843</v>
+        <f t="shared" si="73"/>
+        <v>162.35913306931968</v>
       </c>
       <c r="DE16" s="1">
-        <f t="shared" si="70"/>
-        <v>208.63449328867046</v>
+        <f t="shared" si="73"/>
+        <v>160.73554173862649</v>
       </c>
       <c r="DF16" s="1">
-        <f t="shared" si="70"/>
-        <v>206.54814835578375</v>
+        <f t="shared" si="73"/>
+        <v>159.12818632124024</v>
       </c>
       <c r="DG16" s="1">
-        <f t="shared" ref="DG16:FF16" si="71">DF16*(1+$AV$21)</f>
-        <v>204.48266687222591</v>
+        <f t="shared" ref="DG16:FF16" si="74">DF16*(1+$AV$21)</f>
+        <v>157.53690445802783</v>
       </c>
       <c r="DH16" s="1">
-        <f t="shared" si="71"/>
-        <v>202.43784020350364</v>
+        <f t="shared" si="74"/>
+        <v>155.96153541344756</v>
       </c>
       <c r="DI16" s="1">
-        <f t="shared" si="71"/>
-        <v>200.4134618014686</v>
+        <f t="shared" si="74"/>
+        <v>154.40192005931308</v>
       </c>
       <c r="DJ16" s="1">
-        <f t="shared" si="71"/>
-        <v>198.40932718345391</v>
+        <f t="shared" si="74"/>
+        <v>152.85790085871994</v>
       </c>
       <c r="DK16" s="1">
-        <f t="shared" si="71"/>
-        <v>196.42523391161936</v>
+        <f t="shared" si="74"/>
+        <v>151.32932185013274</v>
       </c>
       <c r="DL16" s="1">
-        <f t="shared" si="71"/>
-        <v>194.46098157250316</v>
+        <f t="shared" si="74"/>
+        <v>149.81602863163141</v>
       </c>
       <c r="DM16" s="1">
-        <f t="shared" si="71"/>
-        <v>192.51637175677811</v>
+        <f t="shared" si="74"/>
+        <v>148.31786834531511</v>
       </c>
       <c r="DN16" s="1">
-        <f t="shared" si="71"/>
-        <v>190.59120803921033</v>
+        <f t="shared" si="74"/>
+        <v>146.83468966186194</v>
       </c>
       <c r="DO16" s="1">
-        <f t="shared" si="71"/>
-        <v>188.68529595881822</v>
+        <f t="shared" si="74"/>
+        <v>145.36634276524333</v>
       </c>
       <c r="DP16" s="1">
-        <f t="shared" si="71"/>
-        <v>186.79844299923002</v>
+        <f t="shared" si="74"/>
+        <v>143.9126793375909</v>
       </c>
       <c r="DQ16" s="1">
-        <f t="shared" si="71"/>
-        <v>184.93045856923771</v>
+        <f t="shared" si="74"/>
+        <v>142.47355254421498</v>
       </c>
       <c r="DR16" s="1">
-        <f t="shared" si="71"/>
-        <v>183.08115398354533</v>
+        <f t="shared" si="74"/>
+        <v>141.04881701877284</v>
       </c>
       <c r="DS16" s="1">
-        <f t="shared" si="71"/>
-        <v>181.25034244370988</v>
+        <f t="shared" si="74"/>
+        <v>139.6383288485851</v>
       </c>
       <c r="DT16" s="1">
-        <f t="shared" si="71"/>
-        <v>179.43783901927279</v>
+        <f t="shared" si="74"/>
+        <v>138.24194556009925</v>
       </c>
       <c r="DU16" s="1">
-        <f t="shared" si="71"/>
-        <v>177.64346062908007</v>
+        <f t="shared" si="74"/>
+        <v>136.85952610449826</v>
       </c>
       <c r="DV16" s="1">
-        <f t="shared" si="71"/>
-        <v>175.86702602278928</v>
+        <f t="shared" si="74"/>
+        <v>135.49093084345327</v>
       </c>
       <c r="DW16" s="1">
-        <f t="shared" si="71"/>
-        <v>174.10835576256139</v>
+        <f t="shared" si="74"/>
+        <v>134.13602153501873</v>
       </c>
       <c r="DX16" s="1">
-        <f t="shared" si="71"/>
-        <v>172.36727220493577</v>
+        <f t="shared" si="74"/>
+        <v>132.79466131966853</v>
       </c>
       <c r="DY16" s="1">
-        <f t="shared" si="71"/>
-        <v>170.6435994828864</v>
+        <f t="shared" si="74"/>
+        <v>131.46671470647186</v>
       </c>
       <c r="DZ16" s="1">
-        <f t="shared" si="71"/>
-        <v>168.93716348805754</v>
+        <f t="shared" si="74"/>
+        <v>130.15204755940715</v>
       </c>
       <c r="EA16" s="1">
-        <f t="shared" si="71"/>
-        <v>167.24779185317695</v>
+        <f t="shared" si="74"/>
+        <v>128.85052708381309</v>
       </c>
       <c r="EB16" s="1">
-        <f t="shared" si="71"/>
-        <v>165.57531393464518</v>
+        <f t="shared" si="74"/>
+        <v>127.56202181297496</v>
       </c>
       <c r="EC16" s="1">
-        <f t="shared" si="71"/>
-        <v>163.91956079529874</v>
+        <f t="shared" si="74"/>
+        <v>126.28640159484522</v>
       </c>
       <c r="ED16" s="1">
-        <f t="shared" si="71"/>
-        <v>162.28036518734575</v>
+        <f t="shared" si="74"/>
+        <v>125.02353757889676</v>
       </c>
       <c r="EE16" s="1">
-        <f t="shared" si="71"/>
-        <v>160.6575615354723</v>
+        <f t="shared" si="74"/>
+        <v>123.77330220310779</v>
       </c>
       <c r="EF16" s="1">
-        <f t="shared" si="71"/>
-        <v>159.05098592011757</v>
+        <f t="shared" si="74"/>
+        <v>122.53556918107671</v>
       </c>
       <c r="EG16" s="1">
-        <f t="shared" si="71"/>
-        <v>157.46047606091639</v>
+        <f t="shared" si="74"/>
+        <v>121.31021348926595</v>
       </c>
       <c r="EH16" s="1">
-        <f t="shared" si="71"/>
-        <v>155.88587130030723</v>
+        <f t="shared" si="74"/>
+        <v>120.09711135437328</v>
       </c>
       <c r="EI16" s="1">
-        <f t="shared" si="71"/>
-        <v>154.32701258730415</v>
+        <f t="shared" si="74"/>
+        <v>118.89614024082955</v>
       </c>
       <c r="EJ16" s="1">
-        <f t="shared" si="71"/>
-        <v>152.7837424614311</v>
+        <f t="shared" si="74"/>
+        <v>117.70717883842126</v>
       </c>
       <c r="EK16" s="1">
-        <f t="shared" si="71"/>
-        <v>151.25590503681678</v>
+        <f t="shared" si="74"/>
+        <v>116.53010705003705</v>
       </c>
       <c r="EL16" s="1">
-        <f t="shared" si="71"/>
-        <v>149.74334598644862</v>
+        <f t="shared" si="74"/>
+        <v>115.36480597953667</v>
       </c>
       <c r="EM16" s="1">
-        <f t="shared" si="71"/>
-        <v>148.24591252658414</v>
+        <f t="shared" si="74"/>
+        <v>114.2111579197413</v>
       </c>
       <c r="EN16" s="1">
-        <f t="shared" si="71"/>
-        <v>146.76345340131829</v>
+        <f t="shared" si="74"/>
+        <v>113.06904634054388</v>
       </c>
       <c r="EO16" s="1">
-        <f t="shared" si="71"/>
-        <v>145.29581886730512</v>
+        <f t="shared" si="74"/>
+        <v>111.93835587713843</v>
       </c>
       <c r="EP16" s="1">
-        <f t="shared" si="71"/>
-        <v>143.84286067863206</v>
+        <f t="shared" si="74"/>
+        <v>110.81897231836705</v>
       </c>
       <c r="EQ16" s="1">
-        <f t="shared" si="71"/>
-        <v>142.40443207184575</v>
+        <f t="shared" si="74"/>
+        <v>109.71078259518337</v>
       </c>
       <c r="ER16" s="1">
-        <f t="shared" si="71"/>
-        <v>140.9803877511273</v>
+        <f t="shared" si="74"/>
+        <v>108.61367476923154</v>
       </c>
       <c r="ES16" s="1">
-        <f t="shared" si="71"/>
-        <v>139.57058387361602</v>
+        <f t="shared" si="74"/>
+        <v>107.52753802153921</v>
       </c>
       <c r="ET16" s="1">
-        <f t="shared" si="71"/>
-        <v>138.17487803487987</v>
+        <f t="shared" si="74"/>
+        <v>106.45226264132383</v>
       </c>
       <c r="EU16" s="1">
-        <f t="shared" si="71"/>
-        <v>136.79312925453107</v>
+        <f t="shared" si="74"/>
+        <v>105.38774001491059</v>
       </c>
       <c r="EV16" s="1">
-        <f t="shared" si="71"/>
-        <v>135.42519796198576</v>
+        <f t="shared" si="74"/>
+        <v>104.33386261476149</v>
       </c>
       <c r="EW16" s="1">
-        <f t="shared" si="71"/>
-        <v>134.07094598236591</v>
+        <f t="shared" si="74"/>
+        <v>103.29052398861387</v>
       </c>
       <c r="EX16" s="1">
-        <f t="shared" si="71"/>
-        <v>132.73023652254224</v>
+        <f t="shared" si="74"/>
+        <v>102.25761874872774</v>
       </c>
       <c r="EY16" s="1">
-        <f t="shared" si="71"/>
-        <v>131.40293415731682</v>
+        <f t="shared" si="74"/>
+        <v>101.23504256124046</v>
       </c>
       <c r="EZ16" s="1">
-        <f t="shared" si="71"/>
-        <v>130.08890481574366</v>
+        <f t="shared" si="74"/>
+        <v>100.22269213562805</v>
       </c>
       <c r="FA16" s="1">
-        <f t="shared" si="71"/>
-        <v>128.78801576758622</v>
+        <f t="shared" si="74"/>
+        <v>99.220465214271769</v>
       </c>
       <c r="FB16" s="1">
-        <f t="shared" si="71"/>
-        <v>127.50013560991036</v>
+        <f t="shared" si="74"/>
+        <v>98.228260562129051</v>
       </c>
       <c r="FC16" s="1">
-        <f t="shared" si="71"/>
-        <v>126.22513425381125</v>
+        <f t="shared" si="74"/>
+        <v>97.245977956507758</v>
       </c>
       <c r="FD16" s="1">
-        <f t="shared" si="71"/>
-        <v>124.96288291127314</v>
+        <f t="shared" si="74"/>
+        <v>96.273518176942673</v>
       </c>
       <c r="FE16" s="1">
-        <f t="shared" si="71"/>
-        <v>123.7132540821604</v>
+        <f t="shared" si="74"/>
+        <v>95.310782995173241</v>
       </c>
       <c r="FF16" s="1">
-        <f t="shared" si="71"/>
-        <v>122.4761215413388</v>
+        <f t="shared" si="74"/>
+        <v>94.357675165221508</v>
       </c>
     </row>
-    <row r="17" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>2</v>
       </c>
@@ -3528,10 +3623,22 @@
       <c r="V17" s="5">
         <v>60.7</v>
       </c>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="5"/>
+      <c r="W17" s="5">
+        <f>59.8</f>
+        <v>59.8</v>
+      </c>
+      <c r="X17" s="5">
+        <f>58.8</f>
+        <v>58.8</v>
+      </c>
+      <c r="Y17" s="5">
+        <f>58.8</f>
+        <v>58.8</v>
+      </c>
+      <c r="Z17" s="5">
+        <f>58.8</f>
+        <v>58.8</v>
+      </c>
       <c r="AB17" s="5">
         <v>183.4</v>
       </c>
@@ -3554,127 +3661,150 @@
         <v>60.7</v>
       </c>
       <c r="AI17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AJ17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AK17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AL17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AM17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AN17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AO17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AP17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AQ17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AR17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
       <c r="AS17" s="5">
-        <v>60.7</v>
+        <f>58.8</f>
+        <v>58.8</v>
       </c>
     </row>
-    <row r="18" spans="2:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:H18" si="72">C16/C17</f>
+        <f t="shared" ref="C18:H18" si="75">C16/C17</f>
         <v>-0.27917121046892046</v>
       </c>
       <c r="D18" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>-8.6695747001090478E-2</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>-0.20883315158124316</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>-1.7993456924754608E-2</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>-0.33151581243184308</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>3.5441657579062195E-2</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" ref="I18:J18" si="73">I16/I17</f>
+        <f t="shared" ref="I18:J18" si="76">I16/I17</f>
         <v>-0.80207197382769879</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>1.4675324675324675</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" ref="K18:L18" si="74">K16/K17</f>
+        <f t="shared" ref="K18:L18" si="77">K16/K17</f>
         <v>-19.012987012987015</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>-11.233766233766232</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" ref="M18" si="75">M16/M17</f>
+        <f t="shared" ref="M18" si="78">M16/M17</f>
         <v>1.6233766233765958E-2</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" ref="N18" si="76">N16/N17</f>
+        <f t="shared" ref="N18" si="79">N16/N17</f>
         <v>-0.53896103896103853</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" ref="O18:P18" si="77">O16/O17</f>
+        <f t="shared" ref="O18:P18" si="80">O16/O17</f>
         <v>-6.3311688311688305E-2</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>-2.9220779220778915E-2</v>
       </c>
       <c r="Q18" s="7">
-        <f t="shared" ref="Q18" si="78">Q16/Q17</f>
+        <f t="shared" ref="Q18" si="81">Q16/Q17</f>
         <v>-4.0584415584415702E-2</v>
       </c>
       <c r="R18" s="7">
-        <f t="shared" ref="R18" si="79">R16/R17</f>
+        <f t="shared" ref="R18" si="82">R16/R17</f>
         <v>-0.19805194805194801</v>
       </c>
       <c r="S18" s="7">
-        <f t="shared" ref="S18:V18" si="80">S16/S17</f>
+        <f t="shared" ref="S18:V18" si="83">S16/S17</f>
         <v>4.7077922077921552E-2</v>
       </c>
       <c r="T18" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>-2.3064250411862015E-2</v>
       </c>
       <c r="U18" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>-0.21252059308072441</v>
       </c>
       <c r="V18" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>0.55024711696869721</v>
       </c>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
+      <c r="W18" s="7">
+        <f t="shared" ref="W18:Z18" si="84">W16/W17</f>
+        <v>-0.32775919732441472</v>
+      </c>
+      <c r="X18" s="7">
+        <f t="shared" si="84"/>
+        <v>-0.84863945578231303</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" si="84"/>
+        <v>-0.17735950680272067</v>
+      </c>
+      <c r="Z18" s="7">
+        <f t="shared" si="84"/>
+        <v>-0.17212739795918386</v>
+      </c>
       <c r="AB18" s="7">
         <f>AB16/AB17</f>
         <v>-0.21646673936750277</v>
@@ -3696,59 +3826,59 @@
         <v>-10.334787350054526</v>
       </c>
       <c r="AG18" s="7">
-        <f t="shared" ref="AG18:AO18" si="81">AG16/AG17</f>
+        <f t="shared" ref="AG18:AO18" si="85">AG16/AG17</f>
         <v>-0.11123227917121062</v>
       </c>
       <c r="AH18" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>0.362438220757825</v>
       </c>
       <c r="AI18" s="7">
-        <f t="shared" si="81"/>
-        <v>0.81658813838549971</v>
+        <f t="shared" si="85"/>
+        <v>2.3568430272108838</v>
       </c>
       <c r="AJ18" s="7">
-        <f t="shared" si="81"/>
-        <v>3.7172894456342642</v>
+        <f t="shared" si="85"/>
+        <v>2.984565741496596</v>
       </c>
       <c r="AK18" s="7">
-        <f t="shared" si="81"/>
-        <v>4.1901600593574919</v>
+        <f t="shared" si="85"/>
+        <v>3.515127947755099</v>
       </c>
       <c r="AL18" s="7">
-        <f t="shared" si="81"/>
-        <v>4.4800138881187763</v>
+        <f t="shared" si="85"/>
+        <v>3.841574418274825</v>
       </c>
       <c r="AM18" s="7">
-        <f t="shared" si="81"/>
-        <v>4.8199948150244394</v>
+        <f t="shared" si="85"/>
+        <v>4.2143854465189623</v>
       </c>
       <c r="AN18" s="7">
-        <f t="shared" si="81"/>
-        <v>5.1366597274528516</v>
+        <f t="shared" si="85"/>
+        <v>4.5541413872573813</v>
       </c>
       <c r="AO18" s="7">
-        <f t="shared" si="81"/>
-        <v>5.4358533460808056</v>
+        <f t="shared" si="85"/>
+        <v>4.7223755274054637</v>
       </c>
       <c r="AP18" s="7">
-        <f t="shared" ref="AP18:AS18" si="82">AP16/AP17</f>
-        <v>5.7222836565156152</v>
+        <f t="shared" ref="AP18:AS18" si="86">AP16/AP17</f>
+        <v>4.8668438500239048</v>
       </c>
       <c r="AQ18" s="7">
-        <f t="shared" si="82"/>
-        <v>5.999750142846092</v>
+        <f t="shared" si="86"/>
+        <v>4.9923356153724869</v>
       </c>
       <c r="AR18" s="7">
-        <f t="shared" si="82"/>
-        <v>6.2713264153069881</v>
+        <f t="shared" si="86"/>
+        <v>5.102681180225745</v>
       </c>
       <c r="AS18" s="7">
-        <f t="shared" si="82"/>
-        <v>6.5395063540310749</v>
+        <f t="shared" si="86"/>
+        <v>5.2009435251089826</v>
       </c>
     </row>
-    <row r="20" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>34</v>
       </c>
@@ -3761,80 +3891,80 @@
         <v>4.8333333333333339E-2</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" ref="H20:J20" si="83">H3/D3-1</f>
+        <f t="shared" ref="H20:J20" si="87">H3/D3-1</f>
         <v>0.12697947214076244</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>-5.3445850914204396E-3</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>3.780718336483968E-3</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" ref="K20" si="84">K3/G3-1</f>
+        <f t="shared" ref="K20" si="88">K3/G3-1</f>
         <v>-2.5702172760996289E-2</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" ref="L20" si="85">L3/H3-1</f>
+        <f t="shared" ref="L20" si="89">L3/H3-1</f>
         <v>-1.4051522248243686E-2</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" ref="M20" si="86">M3/I3-1</f>
+        <f t="shared" ref="M20" si="90">M3/I3-1</f>
         <v>3.5067873303167296E-2</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" ref="N20" si="87">N3/J3-1</f>
+        <f t="shared" ref="N20" si="91">N3/J3-1</f>
         <v>3.201506591337111E-2</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" ref="O20" si="88">O3/K3-1</f>
+        <f t="shared" ref="O20" si="92">O3/K3-1</f>
         <v>5.4664128365515374E-2</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" ref="P20" si="89">P3/L3-1</f>
+        <f t="shared" ref="P20" si="93">P3/L3-1</f>
         <v>6.1757719714964354E-2</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20" si="90">Q3/M3-1</f>
+        <f t="shared" ref="Q20" si="94">Q3/M3-1</f>
         <v>8.306010928961749E-2</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" ref="R20" si="91">R3/N3-1</f>
+        <f t="shared" ref="R20" si="95">R3/N3-1</f>
         <v>8.0552659019812234E-2</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20" si="92">S3/O3-1</f>
+        <f t="shared" ref="S20" si="96">S3/O3-1</f>
         <v>7.7101598762248535E-2</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="93">T3/P3-1</f>
+        <f t="shared" ref="T20" si="97">T3/P3-1</f>
         <v>9.346259010688529E-2</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="94">U3/Q3-1</f>
+        <f t="shared" ref="U20" si="98">U3/Q3-1</f>
         <v>7.7447023208879973E-2</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20" si="95">V3/R3-1</f>
+        <f t="shared" ref="V20" si="99">V3/R3-1</f>
         <v>1.351025331724931E-2</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" ref="W20" si="96">W3/S3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="W20" si="100">W3/S3-1</f>
+        <v>-3.9980847498204408E-2</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20" si="97">X3/T3-1</f>
+        <f t="shared" ref="X20" si="101">X3/T3-1</f>
+        <v>-2.659695385314842E-2</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" ref="Y20" si="102">Y3/U3-1</f>
+        <v>-1.0000000000000009E-2</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" ref="Z20" si="103">Z3/V3-1</f>
         <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="98">Y3/U3-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="99">Z3/V3-1</f>
-        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB20" s="9"/>
       <c r="AC20" s="9">
@@ -3842,88 +3972,88 @@
         <v>0.24318400981853228</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20:AO20" si="100">AD3/AC3-1</f>
+        <f t="shared" ref="AD20:AO20" si="104">AD3/AC3-1</f>
         <v>5.9234186587688864E-3</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>4.2411496670171855E-2</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>6.1869535978478218E-3</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>7.0044111749766103E-2</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>6.4834478450968014E-2</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" si="100"/>
-        <v>1.7419638667292237E-2</v>
+        <f t="shared" si="104"/>
+        <v>-1.6699906147348731E-2</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN20" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO20" s="9">
-        <f t="shared" si="100"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="104"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP20" s="9">
-        <f t="shared" ref="AP20" si="101">AP3/AO3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AP20" si="105">AP3/AO3-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ20" s="9">
-        <f t="shared" ref="AQ20" si="102">AQ3/AP3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AQ20" si="106">AQ3/AP3-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR20" s="9">
-        <f t="shared" ref="AR20" si="103">AR3/AQ3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AR20" si="107">AR3/AQ3-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS20" s="9">
-        <f t="shared" ref="AS20" si="104">AS3/AR3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AS20" si="108">AS3/AR3-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:F21" si="105">C5/C3</f>
+        <f t="shared" ref="C21:F21" si="109">C5/C3</f>
         <v>0.64055555555555554</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>0.62991202346041064</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>0.61884669479606191</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>0.61166621658115039</v>
       </c>
       <c r="G21" s="9">
@@ -3931,151 +4061,151 @@
         <v>0.59989401165871747</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" ref="H21:J21" si="106">H5/H3</f>
+        <f t="shared" ref="H21:J21" si="110">H5/H3</f>
         <v>0.59458756180067651</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>0.59021493212669685</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>0.60156039817056761</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" ref="K21:V21" si="107">K5/K3</f>
+        <f t="shared" ref="K21:V21" si="111">K5/K3</f>
         <v>0.59994560783247208</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.58036421219319079</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.5852459016393442</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.59306569343065696</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.59025270758122739</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.58588118319661942</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.58602421796165494</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.5811821471652594</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.59205171175484794</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.58217776767447138</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.58300163896043089</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.5631992382766009</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21:Z21" si="108">W5/W3</f>
+        <f t="shared" ref="W21:Z21" si="112">W5/W3</f>
+        <v>0.56558603491271819</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" si="112"/>
+        <v>0.55581503970107426</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" si="112"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="X21" s="9">
-        <f t="shared" si="108"/>
+      <c r="Z21" s="9">
+        <f t="shared" si="112"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="Y21" s="9">
-        <f t="shared" si="108"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="108"/>
-        <v>0.56000000000000005</v>
-      </c>
       <c r="AB21" s="9">
-        <f t="shared" ref="AB21:AO21" si="109">AB5/AB3</f>
+        <f t="shared" ref="AB21:AO21" si="113">AB5/AB3</f>
         <v>0.65749101428947132</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.64128058670051469</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.62509638976515947</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.59663752521856084</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.58962705520652314</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.58575890068707059</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.58012670107930553</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="109"/>
-        <v>0.6</v>
+        <f t="shared" si="113"/>
+        <v>0.56026725048170711</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AN21" s="9">
+        <f t="shared" si="113"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AO21" s="9">
+        <f t="shared" si="113"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AP21" s="9">
+        <f t="shared" ref="AP21:AS21" si="114">AP5/AP3</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AQ21" s="9">
+        <f t="shared" si="114"/>
         <v>0.58000000000000007</v>
       </c>
-      <c r="AN21" s="9">
-        <f t="shared" si="109"/>
+      <c r="AR21" s="9">
+        <f t="shared" si="114"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AO21" s="9">
-        <f t="shared" si="109"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AP21" s="9">
-        <f t="shared" ref="AP21:AS21" si="110">AP5/AP3</f>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AQ21" s="9">
-        <f t="shared" si="110"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AR21" s="9">
-        <f t="shared" si="110"/>
-        <v>0.57999999999999996</v>
-      </c>
       <c r="AS21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AU21" t="s">
@@ -4085,24 +4215,24 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="22" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:F22" si="111">C10/C3</f>
+        <f t="shared" ref="C22:F22" si="115">C10/C3</f>
         <v>-4.3888888888888901E-2</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>9.8240469208211167E-2</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>-1.1251758087201122E-2</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>7.3453956251687824E-2</v>
       </c>
       <c r="G22" s="9">
@@ -4110,152 +4240,152 @@
         <v>-9.7244303126656134E-2</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:J22" si="112">H10/H3</f>
+        <f t="shared" ref="H22:J22" si="116">H10/H3</f>
         <v>0.10278428311215199</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>-0.85152714932126683</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>7.8019908528383086E-2</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" ref="K22:V22" si="113">K10/K3</f>
+        <f t="shared" ref="K22:V22" si="117">K10/K3</f>
         <v>-3.240957302148491</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>-1.8558986539984164</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>1.2841530054644761E-2</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>4.7705943691345218E-2</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>8.9994842702423902E-2</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>8.5011185682326657E-2</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>0.10898082744702318</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>0.11145958986731001</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>7.8525257361742803E-2</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>8.297340304614681E-2</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>8.054319831421218E-2</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>7.0221375862889651E-2</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22:Z22" si="114">W10/W3</f>
-        <v>0</v>
+        <f t="shared" ref="W22:Z22" si="118">W10/W3</f>
+        <v>2.5436408977556117E-2</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="114"/>
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>4.834189631013544E-2</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="114"/>
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>5.208341906539056E-2</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="114"/>
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>5.2665961192643891E-2</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22:AO22" si="115">AB10/AB3</f>
+        <f t="shared" ref="AB22:AO22" si="119">AB10/AB3</f>
         <v>0.1016042780748663</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="119"/>
         <v>3.6527748395740661E-2</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="119"/>
         <v>1.3810024535576637E-2</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="119"/>
         <v>-0.1811028917283119</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="119"/>
         <v>-1.2511027937441521</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="119"/>
         <v>9.9000624609618976E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="119"/>
         <v>7.8132332238385727E-2</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="115"/>
-        <v>9.0028521236992523E-2</v>
+        <f t="shared" si="119"/>
+        <v>0.1812893642659858</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.20758737671893498</v>
+        <f t="shared" si="119"/>
+        <v>0.19470672686820628</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.21408099324815416</v>
+        <f t="shared" si="119"/>
+        <v>0.20111459166901388</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.21411901434952296</v>
+        <f t="shared" si="119"/>
+        <v>0.2011856229398217</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.21773683519769366</v>
+        <f t="shared" si="119"/>
+        <v>0.20495694114474164</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.22131556928914869</v>
+        <f t="shared" si="119"/>
+        <v>0.20868452661081097</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.22485602546560562</v>
+        <f t="shared" si="119"/>
+        <v>0.2087296983523701</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" ref="AP22:AS22" si="116">AP10/AP3</f>
-        <v>0.22835895456387595</v>
+        <f t="shared" ref="AP22:AS22" si="120">AP10/AP3</f>
+        <v>0.20876995039930396</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="116"/>
-        <v>0.23182505587572833</v>
+        <f t="shared" si="120"/>
+        <v>0.20880581855993824</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="116"/>
-        <v>0.23525498285133659</v>
+        <f t="shared" si="120"/>
+        <v>0.20883778028723599</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="116"/>
-        <v>0.23864934813527208</v>
+        <f t="shared" si="120"/>
+        <v>0.20886626103433301</v>
       </c>
       <c r="AU22" t="s">
         <v>39</v>
@@ -4264,7 +4394,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>37</v>
       </c>
@@ -4277,159 +4407,159 @@
         <v>0.65106382978723398</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:J23" si="117">H6/D6-1</f>
+        <f t="shared" ref="H23:J23" si="121">H6/D6-1</f>
         <v>8.2375478927203094E-2</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="121"/>
         <v>-1.6829052258635957E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="121"/>
         <v>-3.1273836765827623E-2</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" ref="K23" si="118">K6/G6-1</f>
+        <f t="shared" ref="K23" si="122">K6/G6-1</f>
         <v>-0.32680412371134027</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" ref="L23" si="119">L6/H6-1</f>
+        <f t="shared" ref="L23" si="123">L6/H6-1</f>
         <v>0.19203539823008842</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" ref="M23" si="120">M6/I6-1</f>
+        <f t="shared" ref="M23" si="124">M6/I6-1</f>
         <v>0.19189189189189193</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" ref="N23" si="121">N6/J6-1</f>
+        <f t="shared" ref="N23" si="125">N6/J6-1</f>
         <v>7.8740157480315043E-2</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" ref="O23" si="122">O6/K6-1</f>
+        <f t="shared" ref="O23" si="126">O6/K6-1</f>
         <v>-1.761102603369058E-2</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" ref="P23" si="123">P6/L6-1</f>
+        <f t="shared" ref="P23" si="127">P6/L6-1</f>
         <v>-8.1662954714178948E-3</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" ref="Q23" si="124">Q6/M6-1</f>
+        <f t="shared" ref="Q23" si="128">Q6/M6-1</f>
         <v>-8.3900226757369634E-2</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" ref="R23" si="125">R6/N6-1</f>
+        <f t="shared" ref="R23" si="129">R6/N6-1</f>
         <v>-8.7591240875912413E-2</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23" si="126">S6/O6-1</f>
+        <f t="shared" ref="S23" si="130">S6/O6-1</f>
         <v>0.12860483242400633</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" ref="T23" si="127">T6/P6-1</f>
+        <f t="shared" ref="T23" si="131">T6/P6-1</f>
         <v>0.12350299401197606</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" ref="U23" si="128">U6/Q6-1</f>
+        <f t="shared" ref="U23" si="132">U6/Q6-1</f>
         <v>0.18729372937293731</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" ref="V23" si="129">V6/R6-1</f>
+        <f t="shared" ref="V23" si="133">V6/R6-1</f>
         <v>9.4400000000000039E-2</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" ref="W23" si="130">W6/S6-1</f>
-        <v>4.030386740330183E-4</v>
+        <f t="shared" ref="W23" si="134">W6/S6-1</f>
+        <v>-3.4530386740331487E-2</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" ref="X23" si="131">X6/T6-1</f>
-        <v>6.4067954696869212E-3</v>
+        <f t="shared" ref="X23" si="135">X6/T6-1</f>
+        <v>-4.1972018654230392E-2</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" ref="Y23" si="132">Y6/U6-1</f>
-        <v>2.931396803335673E-2</v>
+        <f t="shared" ref="Y23" si="136">Y6/U6-1</f>
+        <v>-9.5997220291865748E-4</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23" si="133">Z6/V6-1</f>
-        <v>6.4990350877192515E-2</v>
+        <f t="shared" ref="Z23" si="137">Z6/V6-1</f>
+        <v>5.4549269005847556E-2</v>
       </c>
       <c r="AB23" s="9"/>
       <c r="AC23" s="9">
-        <f t="shared" ref="AC23:AO23" si="134">AC6/AB6-1</f>
+        <f t="shared" ref="AC23:AO23" si="138">AC6/AB6-1</f>
         <v>0.29561403508771944</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>5.1455653351387909E-2</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>0.16977892251556126</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>-1.9082568807339606E-2</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>-4.9569771791993955E-2</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>0.132847864593584</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP23" s="9">
-        <f t="shared" ref="AP23" si="135">AP6/AO6-1</f>
+        <f t="shared" ref="AP23" si="139">AP6/AO6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ23" s="9">
-        <f t="shared" ref="AQ23" si="136">AQ6/AP6-1</f>
+        <f t="shared" ref="AQ23" si="140">AQ6/AP6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR23" s="9">
-        <f t="shared" ref="AR23" si="137">AR6/AQ6-1</f>
+        <f t="shared" ref="AR23" si="141">AR6/AQ6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS23" s="9">
-        <f t="shared" ref="AS23" si="138">AS6/AR6-1</f>
+        <f t="shared" ref="AS23" si="142">AS6/AR6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU23" t="s">
         <v>40</v>
       </c>
       <c r="AV23" s="5">
-        <f>NPV(AV22,AH16:FF16)</f>
-        <v>3103.2396140817746</v>
+        <f>NPV(AV22,AI16:FF16)</f>
+        <v>2764.3975280071254</v>
       </c>
     </row>
-    <row r="24" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>60</v>
       </c>
@@ -4438,195 +4568,195 @@
         <v>0.3263888888888889</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:V24" si="139">D6/D3</f>
+        <f t="shared" ref="D24:V24" si="143">D6/D3</f>
         <v>0.30615835777126099</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.31758087201125179</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.35403726708074529</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.51404345521992589</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.29404111371324487</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.31391402714932126</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.34167339252085016</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.3551808539570302</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.35550277117973078</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.36147540983606563</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.3571428571428571</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.33084063950489945</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.33209047974148642</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.30575176589303737</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.30156815440289503</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.34666028249940151</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.34121391225278475</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.33692343713416062</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.32563675315401108</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" ref="W24:Z24" si="140">W6/W3</f>
+        <f t="shared" ref="W24:Z24" si="144">W6/W3</f>
+        <v>0.34862842892768081</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" si="144"/>
+        <v>0.33582438113031299</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="144"/>
         <v>0.34</v>
       </c>
-      <c r="X24" s="9">
-        <f t="shared" si="140"/>
-        <v>0.34000000000000008</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="140"/>
+      <c r="Z24" s="9">
+        <f t="shared" si="144"/>
         <v>0.34</v>
       </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="140"/>
-        <v>0.34</v>
-      </c>
       <c r="AB24" s="9">
-        <f t="shared" ref="AB24:AS24" si="141">AB6/AB3</f>
+        <f t="shared" ref="AB24:AS24" si="145">AB6/AB3</f>
         <v>0.29981590251599893</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="145"/>
         <v>0.31246033425005293</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="145"/>
         <v>0.32660357518401678</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="145"/>
         <v>0.36650975117686613</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="145"/>
         <v>0.35730517310519982</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="145"/>
         <v>0.31736414740787006</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="145"/>
         <v>0.33763491318629751</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.35508392346599627</v>
+        <f t="shared" si="145"/>
+        <v>0.36740498589179937</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.36204635333787855</v>
+        <f t="shared" si="145"/>
+        <v>0.37460900522301116</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.36559582739021074</v>
+        <f t="shared" si="145"/>
+        <v>0.37828164252911917</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.36559582739021074</v>
+        <f t="shared" si="145"/>
+        <v>0.37828164252911917</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.36201155457265966</v>
+        <f t="shared" si="145"/>
+        <v>0.37457299897491209</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.35846242168469244</v>
+        <f t="shared" si="145"/>
+        <v>0.37090071467123648</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.35494808421719543</v>
+        <f t="shared" si="145"/>
+        <v>0.37090071467123648</v>
       </c>
       <c r="AP24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.3514682010385955</v>
+        <f t="shared" si="145"/>
+        <v>0.37090071467123653</v>
       </c>
       <c r="AQ24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.34802243436174651</v>
+        <f t="shared" si="145"/>
+        <v>0.37090071467123653</v>
       </c>
       <c r="AR24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.34461044971114108</v>
+        <f t="shared" si="145"/>
+        <v>0.37090071467123653</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" si="141"/>
-        <v>0.3412319158904436</v>
+        <f t="shared" si="145"/>
+        <v>0.37090071467123653</v>
       </c>
       <c r="AU24" t="s">
         <v>41</v>
       </c>
       <c r="AV24" s="5">
         <f>Main!D8</f>
-        <v>-2146.9</v>
+        <v>-2150.2999999999997</v>
       </c>
     </row>
-    <row r="25" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:F25" si="142">C14/C13</f>
+        <f t="shared" ref="C25:F25" si="146">C14/C13</f>
         <v>0.25904486251808967</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>0.14594594594594601</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>0.26930320150659132</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>0.87916666666666687</v>
       </c>
       <c r="G25" s="9">
@@ -4634,162 +4764,165 @@
         <v>8.8588588588588563E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:J25" si="143">H14/H13</f>
+        <f t="shared" ref="H25:J25" si="147">H14/H13</f>
         <v>0.71367521367521347</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="147"/>
         <v>0.34345690040196525</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="147"/>
         <v>-0.26536312849162014</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" ref="K25:V25" si="144">K14/K13</f>
+        <f t="shared" ref="K25:V25" si="148">K14/K13</f>
         <v>3.5743699555262722E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>-2.4578027835356831E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>0.87951807228915846</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>5.9880239520958131E-3</v>
       </c>
       <c r="O25" s="9" t="e">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>1.3749999999999947</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>1.1724137931034488</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>11.166666666666641</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>0.71568627450980615</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>1.3684210526315876</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>0.18354430379746867</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>-1.1273885350318531</v>
       </c>
-      <c r="W25" s="9" t="e">
-        <f t="shared" ref="W25:Z25" si="145">W14/W13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X25" s="9" t="e">
-        <f t="shared" si="145"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y25" s="9" t="e">
-        <f t="shared" si="145"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z25" s="9" t="e">
-        <f t="shared" si="145"/>
-        <v>#DIV/0!</v>
+      <c r="W25" s="9">
+        <f t="shared" ref="W25:Z25" si="149">W14/W13</f>
+        <v>0.13656387665198239</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="149"/>
+        <v>-1.4341463414634144</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="149"/>
+        <v>0.05</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="149"/>
+        <v>0.05</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" ref="AB25:AO25" si="146">AB14/AB13</f>
+        <f t="shared" ref="AB25:AO25" si="150">AB14/AB13</f>
         <v>-0.16422287390029319</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>0.13022888713496433</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>0.31845077998924171</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>0.43529411764705916</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>1.0288818091607038E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>1.9951219512195149</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>-0.58273381294964122</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="146"/>
-        <v>0.25</v>
+        <f t="shared" si="150"/>
+        <v>0.15395791717744969</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="146"/>
-        <v>0.25</v>
+        <f t="shared" si="150"/>
+        <v>0.2</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="146"/>
-        <v>0.25</v>
+        <f t="shared" si="150"/>
+        <v>0.2</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="146"/>
-        <v>0.25</v>
+        <f t="shared" si="150"/>
+        <v>0.2</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="146"/>
-        <v>0.25</v>
+        <f t="shared" si="150"/>
+        <v>0.2</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="146"/>
-        <v>0.25</v>
+        <f t="shared" si="150"/>
+        <v>0.2</v>
       </c>
       <c r="AO25" s="9">
-        <f t="shared" si="146"/>
-        <v>0.25</v>
+        <f t="shared" si="150"/>
+        <v>0.2</v>
       </c>
       <c r="AP25" s="9">
-        <f t="shared" ref="AP25:AS25" si="147">AP14/AP13</f>
-        <v>0.25</v>
+        <f t="shared" ref="AP25:AS25" si="151">AP14/AP13</f>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AQ25" s="9">
-        <f t="shared" si="147"/>
-        <v>0.25</v>
+        <f t="shared" si="151"/>
+        <v>0.2</v>
       </c>
       <c r="AR25" s="9">
-        <f t="shared" si="147"/>
-        <v>0.25</v>
+        <f t="shared" si="151"/>
+        <v>0.2</v>
       </c>
       <c r="AS25" s="9">
-        <f t="shared" si="147"/>
-        <v>0.25</v>
+        <f t="shared" si="151"/>
+        <v>0.2</v>
       </c>
       <c r="AU25" t="s">
         <v>42</v>
       </c>
       <c r="AV25" s="5">
         <f>AV23+AV24</f>
-        <v>956.33961408177447</v>
+        <v>614.09752800712567</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="26" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>47</v>
       </c>
@@ -4798,201 +4931,204 @@
         <v>-0.14222222222222225</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" ref="D26:J26" si="148">D16/D3</f>
+        <f t="shared" ref="D26:J26" si="152">D16/D3</f>
         <v>-4.6627565982404674E-2</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>-0.10773558368495076</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>-8.9116932217121105E-3</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>-0.16110227874933766</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>1.6913869372885783E-2</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>-0.4160067873303166</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>0.24320688727468387</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" ref="K26:V26" si="149">K16/K3</f>
+        <f t="shared" ref="K26:V26" si="153">K16/K3</f>
         <v>-3.1852053304324182</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>-1.826339403536553</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>2.732240437158424E-3</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>-8.6548488008341945E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>-1.0056730273336771E-2</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>-4.4742729306487226E-3</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>-6.3067608476286762E-3</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>-2.9433051869722553E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>6.9427819008857257E-3</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>-3.1825414867015784E-3</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>-3.0203699367829479E-2</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>7.9504879790525909E-2</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" ref="W26:Z26" si="150">W16/W3</f>
-        <v>0</v>
+        <f t="shared" ref="W26:Z26" si="154">W16/W3</f>
+        <v>-4.8877805486284287E-2</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="150"/>
-        <v>0</v>
+        <f t="shared" si="154"/>
+        <v>-0.11653432975245215</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="150"/>
-        <v>0</v>
+        <f t="shared" si="154"/>
+        <v>-2.4664199948442454E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="150"/>
-        <v>0</v>
+        <f t="shared" si="154"/>
+        <v>-2.3853563861504012E-2</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" ref="AB26:AO26" si="151">AB16/AB3</f>
+        <f t="shared" ref="AB26:AO26" si="155">AB16/AB3</f>
         <v>-3.4803191023056027E-2</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>-7.7639094563147992E-2</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>-8.8818787241500122E-2</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>-7.4646940147948773E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>-1.2668092501002541</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>-1.2742036227357919E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>1.2904739558892526E-2</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="151"/>
-        <v>2.8577103333127608E-2</v>
+        <f t="shared" si="155"/>
+        <v>8.2670100755817752E-2</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="151"/>
-        <v>0.12753851175840122</v>
+        <f t="shared" si="155"/>
+        <v>0.10263577986598399</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="151"/>
-        <v>0.14094361533798838</v>
+        <f t="shared" si="155"/>
+        <v>0.11851098365586354</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="151"/>
-        <v>0.14773860130828403</v>
+        <f t="shared" si="155"/>
+        <v>0.12697743332213726</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="151"/>
-        <v>0.15583357072064288</v>
+        <f t="shared" si="155"/>
+        <v>0.13656876285386529</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="151"/>
-        <v>0.16281524855236523</v>
+        <f t="shared" si="155"/>
+        <v>0.1446849836282362</v>
       </c>
       <c r="AO26" s="9">
-        <f t="shared" si="151"/>
-        <v>0.16892029798333769</v>
+        <f t="shared" si="155"/>
+        <v>0.14854433564444802</v>
       </c>
       <c r="AP26" s="9">
-        <f t="shared" ref="AP26:AS26" si="152">AP16/AP3</f>
-        <v>0.17433449093495687</v>
+        <f t="shared" ref="AP26:AS26" si="156">AP16/AP3</f>
+        <v>0.15157291913649526</v>
       </c>
       <c r="AQ26" s="9">
-        <f t="shared" si="152"/>
-        <v>0.17920368203085055</v>
+        <f t="shared" si="156"/>
+        <v>0.15394181483336203</v>
       </c>
       <c r="AR26" s="9">
-        <f t="shared" si="152"/>
-        <v>0.18364241616000235</v>
+        <f t="shared" si="156"/>
+        <v>0.15578652461839532</v>
       </c>
       <c r="AS26" s="9">
-        <f t="shared" si="152"/>
-        <v>0.18774067998781005</v>
+        <f t="shared" si="156"/>
+        <v>0.15721436250687595</v>
       </c>
       <c r="AU26" t="s">
         <v>43</v>
       </c>
       <c r="AV26" s="4">
         <f>AV25/AO17</f>
-        <v>15.755183098546532</v>
+        <v>10.443835510325266</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="27" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:50" x14ac:dyDescent="0.3">
       <c r="AU27" t="s">
         <v>44</v>
       </c>
       <c r="AV27" s="4">
         <f>Main!D3</f>
-        <v>14.96</v>
+        <v>13.53</v>
       </c>
     </row>
-    <row r="28" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:50" x14ac:dyDescent="0.3">
       <c r="AU28" s="1" t="s">
         <v>45</v>
       </c>
       <c r="AV28" s="10">
         <f>AV26/AV27-1</f>
-        <v>5.3153950437602404E-2</v>
+        <v>-0.22809789280670612</v>
       </c>
     </row>
-    <row r="29" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:50" x14ac:dyDescent="0.3">
       <c r="AU29" t="s">
         <v>46</v>
       </c>
       <c r="AV29" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/PSFE.xlsx
+++ b/Financial Analysis/PSFE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F606CF-5539-4B26-9D8F-99E262775406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64AA7C5-C399-484D-A764-ADE7B8BB3D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{6F8D5EDB-60E6-4055-AE62-151FC6B3FA19}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{6F8D5EDB-60E6-4055-AE62-151FC6B3FA19}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
     <t>maybe good to do cash flow statement</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -329,13 +329,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -353,7 +353,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15087600" y="0"/>
+          <a:off x="15697200" y="0"/>
           <a:ext cx="0" cy="6111240"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -752,17 +752,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>13.53</v>
+        <v>6.92</v>
       </c>
       <c r="E3" s="3">
-        <v>45888</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45888</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="3">
-        <v>45967</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -783,7 +783,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>795.56399999999996</v>
+        <v>406.89599999999996</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -791,11 +791,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>234.3</f>
-        <v>234.3</v>
+        <f>248.6</f>
+        <v>248.6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -803,11 +803,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>10.2+2374.4</f>
-        <v>2384.6</v>
+        <f>10.2+2486.8</f>
+        <v>2497</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -816,7 +816,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-2150.2999999999997</v>
+        <v>-2248.4</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -825,7 +825,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>2945.8639999999996</v>
+        <v>2655.2960000000003</v>
       </c>
     </row>
   </sheetData>
@@ -1045,8 +1045,7 @@
         <v>428.2</v>
       </c>
       <c r="Y3" s="8">
-        <f>U3*0.99</f>
-        <v>422.82900000000001</v>
+        <v>433.8</v>
       </c>
       <c r="Z3" s="8">
         <f>V3*1.01</f>
@@ -1079,47 +1078,47 @@
       </c>
       <c r="AI3" s="8">
         <f>SUM(W3:Z3)</f>
-        <v>1676.33</v>
+        <v>1687.3009999999999</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.02</f>
-        <v>1709.8565999999998</v>
+        <v>1721.04702</v>
       </c>
       <c r="AK3" s="8">
-        <f t="shared" ref="AK3:AS3" si="0">AJ3*1.02</f>
-        <v>1744.0537319999999</v>
+        <f t="shared" ref="AK3:AN3" si="0">AJ3*1.02</f>
+        <v>1755.4679604</v>
       </c>
       <c r="AL3" s="8">
         <f t="shared" si="0"/>
-        <v>1778.9348066399998</v>
+        <v>1790.5773196080002</v>
       </c>
       <c r="AM3" s="8">
         <f t="shared" si="0"/>
-        <v>1814.5135027727999</v>
+        <v>1826.3888660001601</v>
       </c>
       <c r="AN3" s="8">
-        <f t="shared" si="0"/>
-        <v>1850.8037728282559</v>
+        <f>AM3*1.01</f>
+        <v>1844.6527546601617</v>
       </c>
       <c r="AO3" s="8">
         <f>AN3*1.01</f>
-        <v>1869.3118105565384</v>
+        <v>1863.0992822067633</v>
       </c>
       <c r="AP3" s="8">
         <f t="shared" ref="AP3:AS3" si="1">AO3*1.01</f>
-        <v>1888.0049286621038</v>
+        <v>1881.7302750288309</v>
       </c>
       <c r="AQ3" s="8">
         <f t="shared" si="1"/>
-        <v>1906.8849779487248</v>
+        <v>1900.5475777791191</v>
       </c>
       <c r="AR3" s="8">
         <f t="shared" si="1"/>
-        <v>1925.953827728212</v>
+        <v>1919.5530535569103</v>
       </c>
       <c r="AS3" s="8">
         <f t="shared" si="1"/>
-        <v>1945.2133660054942</v>
+        <v>1938.7485840924794</v>
       </c>
     </row>
     <row r="4" spans="2:162" x14ac:dyDescent="0.3">
@@ -1194,11 +1193,10 @@
         <v>190.2</v>
       </c>
       <c r="Y4" s="5">
-        <f t="shared" ref="X4:Z4" si="2">Y3-Y5</f>
-        <v>186.04475999999997</v>
+        <v>183</v>
       </c>
       <c r="Z4" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Y4:Z4" si="2">Z3-Z5</f>
         <v>186.69243999999992</v>
       </c>
       <c r="AB4" s="5">
@@ -1227,47 +1225,47 @@
       </c>
       <c r="AI4" s="5">
         <f>SUM(W4:Z4)</f>
-        <v>737.13719999999989</v>
+        <v>734.0924399999999</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" ref="AJ4:AO4" si="3">AJ3-AJ5</f>
-        <v>735.238338</v>
+        <v>740.05021860000011</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="3"/>
-        <v>732.50256744000001</v>
+        <v>737.29654336800013</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="3"/>
-        <v>747.15261878880005</v>
+        <v>752.04247423536003</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="3"/>
-        <v>762.09567116457606</v>
+        <v>767.08332372006726</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="3"/>
-        <v>777.33758458786747</v>
+        <v>774.75415695726792</v>
       </c>
       <c r="AO4" s="5">
         <f t="shared" si="3"/>
-        <v>785.11096043374619</v>
+        <v>782.50169852684076</v>
       </c>
       <c r="AP4" s="5">
         <f t="shared" ref="AP4:AS4" si="4">AP3-AP5</f>
-        <v>792.96207003808377</v>
+        <v>790.3267155121091</v>
       </c>
       <c r="AQ4" s="5">
         <f t="shared" si="4"/>
-        <v>800.89169073846438</v>
+        <v>798.22998266723016</v>
       </c>
       <c r="AR4" s="5">
         <f t="shared" si="4"/>
-        <v>808.90060764584905</v>
+        <v>806.21228249390242</v>
       </c>
       <c r="AS4" s="5">
         <f t="shared" si="4"/>
-        <v>816.98961372230769</v>
+        <v>814.27440531884145</v>
       </c>
     </row>
     <row r="5" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1275,7 +1273,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:X5" si="5">C3-C4</f>
+        <f t="shared" ref="C5:Y5" si="5">C3-C4</f>
         <v>230.6</v>
       </c>
       <c r="D5" s="8">
@@ -1363,11 +1361,11 @@
         <v>238</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" ref="X5:Z5" si="6">Y3*0.56</f>
-        <v>236.78424000000004</v>
+        <f t="shared" si="5"/>
+        <v>250.8</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="Y5:Z5" si="6">Z3*0.56</f>
         <v>237.60855999999995</v>
       </c>
       <c r="AB5" s="8">
@@ -1400,47 +1398,47 @@
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="7"/>
-        <v>939.19280000000003</v>
+        <v>953.20856000000003</v>
       </c>
       <c r="AJ5" s="8">
         <f>AJ3*0.57</f>
-        <v>974.61826199999985</v>
+        <v>980.99680139999987</v>
       </c>
       <c r="AK5" s="8">
         <f>AK3*0.58</f>
-        <v>1011.5511645599998</v>
+        <v>1018.1714170319999</v>
       </c>
       <c r="AL5" s="8">
         <f t="shared" ref="AL5:AS5" si="8">AL3*0.58</f>
-        <v>1031.7821878511998</v>
+        <v>1038.5348453726401</v>
       </c>
       <c r="AM5" s="8">
         <f t="shared" si="8"/>
-        <v>1052.4178316082239</v>
+        <v>1059.3055422800928</v>
       </c>
       <c r="AN5" s="8">
         <f t="shared" si="8"/>
-        <v>1073.4661882403884</v>
+        <v>1069.8985977028938</v>
       </c>
       <c r="AO5" s="8">
         <f t="shared" si="8"/>
-        <v>1084.2008501227922</v>
+        <v>1080.5975836799225</v>
       </c>
       <c r="AP5" s="8">
         <f t="shared" si="8"/>
-        <v>1095.04285862402</v>
+        <v>1091.4035595167218</v>
       </c>
       <c r="AQ5" s="8">
         <f t="shared" si="8"/>
-        <v>1105.9932872102604</v>
+        <v>1102.317595111889</v>
       </c>
       <c r="AR5" s="8">
         <f t="shared" si="8"/>
-        <v>1117.0532200823629</v>
+        <v>1113.3407710630079</v>
       </c>
       <c r="AS5" s="8">
         <f t="shared" si="8"/>
-        <v>1128.2237522831865</v>
+        <v>1124.474178773638</v>
       </c>
     </row>
     <row r="6" spans="2:162" x14ac:dyDescent="0.3">
@@ -1515,12 +1513,11 @@
         <v>143.80000000000001</v>
       </c>
       <c r="Y6" s="5">
-        <f t="shared" ref="X6:Z6" si="9">Y3*0.34</f>
-        <v>143.76186000000001</v>
+        <v>130.1</v>
       </c>
       <c r="Z6" s="5">
-        <f t="shared" si="9"/>
-        <v>144.26233999999997</v>
+        <f>Z3*0.33</f>
+        <v>140.01932999999997</v>
       </c>
       <c r="AB6" s="5">
         <v>342</v>
@@ -1563,31 +1560,31 @@
         <v>672.9383806080001</v>
       </c>
       <c r="AM6" s="5">
-        <f t="shared" ref="AM6:AO6" si="10">AL6*1.01</f>
+        <f t="shared" ref="AM6:AO6" si="9">AL6*1.01</f>
         <v>679.66776441408012</v>
       </c>
       <c r="AN6" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>686.46444205822092</v>
       </c>
       <c r="AO6" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>693.32908647880311</v>
       </c>
       <c r="AP6" s="5">
-        <f t="shared" ref="AP6" si="11">AO6*1.01</f>
+        <f t="shared" ref="AP6" si="10">AO6*1.01</f>
         <v>700.2623773435912</v>
       </c>
       <c r="AQ6" s="5">
-        <f t="shared" ref="AQ6" si="12">AP6*1.01</f>
+        <f t="shared" ref="AQ6" si="11">AP6*1.01</f>
         <v>707.26500111702717</v>
       </c>
       <c r="AR6" s="5">
-        <f t="shared" ref="AR6" si="13">AQ6*1.01</f>
+        <f t="shared" ref="AR6" si="12">AQ6*1.01</f>
         <v>714.33765112819742</v>
       </c>
       <c r="AS6" s="5">
-        <f t="shared" ref="AS6" si="14">AR6*1.01</f>
+        <f t="shared" ref="AS6" si="13">AR6*1.01</f>
         <v>721.48102763947941</v>
       </c>
     </row>
@@ -1663,7 +1660,7 @@
         <v>67.599999999999994</v>
       </c>
       <c r="Y7" s="5">
-        <v>68</v>
+        <v>68.8</v>
       </c>
       <c r="Z7" s="5">
         <v>69</v>
@@ -1810,43 +1807,43 @@
         <v>1.3</v>
       </c>
       <c r="AJ8" s="5">
-        <f t="shared" ref="AJ8:AO8" si="15">AI8*0.9</f>
+        <f t="shared" ref="AJ8:AO8" si="14">AI8*0.9</f>
         <v>1.1700000000000002</v>
       </c>
       <c r="AK8" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0530000000000002</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.94770000000000021</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.85293000000000019</v>
       </c>
       <c r="AN8" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.76763700000000024</v>
       </c>
       <c r="AO8" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.69087330000000025</v>
       </c>
       <c r="AP8" s="5">
-        <f t="shared" ref="AP8" si="16">AO8*0.9</f>
+        <f t="shared" ref="AP8" si="15">AO8*0.9</f>
         <v>0.62178597000000024</v>
       </c>
       <c r="AQ8" s="5">
-        <f t="shared" ref="AQ8" si="17">AP8*0.9</f>
+        <f t="shared" ref="AQ8" si="16">AP8*0.9</f>
         <v>0.55960737300000019</v>
       </c>
       <c r="AR8" s="5">
-        <f t="shared" ref="AR8" si="18">AQ8*0.9</f>
+        <f t="shared" ref="AR8" si="17">AQ8*0.9</f>
         <v>0.50364663570000023</v>
       </c>
       <c r="AS8" s="5">
-        <f t="shared" ref="AS8" si="19">AR8*0.9</f>
+        <f t="shared" ref="AS8" si="18">AR8*0.9</f>
         <v>0.45328197213000021</v>
       </c>
     </row>
@@ -1929,7 +1926,8 @@
         <v>5.9</v>
       </c>
       <c r="Y9" s="5">
-        <v>3</v>
+        <f>12.7+0.2</f>
+        <v>12.899999999999999</v>
       </c>
       <c r="Z9" s="5">
         <v>2</v>
@@ -1963,7 +1961,7 @@
       </c>
       <c r="AI9" s="5">
         <f>SUM(W9:Z9)</f>
-        <v>18.100000000000001</v>
+        <v>28</v>
       </c>
       <c r="AJ9" s="5">
         <v>0</v>
@@ -2001,100 +1999,100 @@
         <v>26</v>
       </c>
       <c r="C10" s="8">
-        <f t="shared" ref="C10:D10" si="20">C5-C6-C7-C8-C9</f>
+        <f t="shared" ref="C10:D10" si="19">C5-C6-C7-C8-C9</f>
         <v>-15.800000000000004</v>
       </c>
       <c r="D10" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>33.500000000000007</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" ref="E10" si="21">E5-E6-E7-E8-E9</f>
+        <f t="shared" ref="E10" si="20">E5-E6-E7-E8-E9</f>
         <v>-3.9999999999999987</v>
       </c>
       <c r="F10" s="8">
-        <f t="shared" ref="F10" si="22">F5-F6-F7-F8-F9</f>
+        <f t="shared" ref="F10" si="21">F5-F6-F7-F8-F9</f>
         <v>27.200000000000003</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" ref="G10:H10" si="23">G5-G6-G7-G8-G9</f>
+        <f t="shared" ref="G10:H10" si="22">G5-G6-G7-G8-G9</f>
         <v>-36.700000000000024</v>
       </c>
       <c r="H10" s="8">
+        <f t="shared" si="22"/>
+        <v>39.500000000000007</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" ref="I10:J10" si="23">I5-I6-I7-I8-I9</f>
+        <v>-301.09999999999997</v>
+      </c>
+      <c r="J10" s="8">
         <f t="shared" si="23"/>
-        <v>39.500000000000007</v>
-      </c>
-      <c r="I10" s="8">
-        <f t="shared" ref="I10:J10" si="24">I5-I6-I7-I8-I9</f>
-        <v>-301.09999999999997</v>
-      </c>
-      <c r="J10" s="8">
+        <v>28.999999999999993</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" ref="K10:L10" si="24">K5-K6-K7-K8-K9</f>
+        <v>-1191.7</v>
+      </c>
+      <c r="L10" s="8">
         <f t="shared" si="24"/>
-        <v>28.999999999999993</v>
-      </c>
-      <c r="K10" s="8">
-        <f t="shared" ref="K10:L10" si="25">K5-K6-K7-K8-K9</f>
-        <v>-1191.7</v>
-      </c>
-      <c r="L10" s="8">
-        <f t="shared" si="25"/>
         <v>-703.19999999999993</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" ref="M10" si="26">M5-M6-M7-M8-M9</f>
+        <f t="shared" ref="M10" si="25">M5-M6-M7-M8-M9</f>
         <v>4.6999999999999824</v>
       </c>
       <c r="N10" s="8">
-        <f t="shared" ref="N10" si="27">N5-N6-N7-N8-N9</f>
+        <f t="shared" ref="N10" si="26">N5-N6-N7-N8-N9</f>
         <v>18.300000000000026</v>
       </c>
       <c r="O10" s="8">
-        <f t="shared" ref="O10:P10" si="28">O5-O6-O7-O8-O9</f>
+        <f t="shared" ref="O10:P10" si="27">O5-O6-O7-O8-O9</f>
         <v>34.899999999999991</v>
       </c>
       <c r="P10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>34.200000000000017</v>
       </c>
       <c r="Q10" s="8">
-        <f t="shared" ref="Q10" si="29">Q5-Q6-Q7-Q8-Q9</f>
+        <f t="shared" ref="Q10" si="28">Q5-Q6-Q7-Q8-Q9</f>
         <v>43.199999999999989</v>
       </c>
       <c r="R10" s="8">
-        <f t="shared" ref="R10" si="30">R5-R6-R7-R8-R9</f>
+        <f t="shared" ref="R10" si="29">R5-R6-R7-R8-R9</f>
         <v>46.2</v>
       </c>
       <c r="S10" s="8">
-        <f t="shared" ref="S10:V10" si="31">S5-S6-S7-S8-S9</f>
+        <f t="shared" ref="S10:V10" si="30">S5-S6-S7-S8-S9</f>
         <v>32.799999999999969</v>
       </c>
       <c r="T10" s="8">
+        <f t="shared" si="30"/>
+        <v>36.499999999999979</v>
+      </c>
+      <c r="U10" s="8">
+        <f t="shared" si="30"/>
+        <v>34.400000000000027</v>
+      </c>
+      <c r="V10" s="8">
+        <f t="shared" si="30"/>
+        <v>29.499999999999932</v>
+      </c>
+      <c r="W10" s="8">
+        <f t="shared" ref="W10:Z10" si="31">W5-W6-W7-W8-W9</f>
+        <v>10.200000000000003</v>
+      </c>
+      <c r="X10" s="8">
         <f t="shared" si="31"/>
-        <v>36.499999999999979</v>
-      </c>
-      <c r="U10" s="8">
+        <v>20.699999999999996</v>
+      </c>
+      <c r="Y10" s="8">
         <f t="shared" si="31"/>
-        <v>34.400000000000027</v>
-      </c>
-      <c r="V10" s="8">
+        <v>39.000000000000021</v>
+      </c>
+      <c r="Z10" s="8">
         <f t="shared" si="31"/>
-        <v>29.499999999999932</v>
-      </c>
-      <c r="W10" s="8">
-        <f t="shared" ref="W10:Z10" si="32">W5-W6-W7-W8-W9</f>
-        <v>10.200000000000003</v>
-      </c>
-      <c r="X10" s="8">
-        <f t="shared" si="32"/>
-        <v>20.699999999999996</v>
-      </c>
-      <c r="Y10" s="8">
-        <f t="shared" si="32"/>
-        <v>22.022380000000027</v>
-      </c>
-      <c r="Z10" s="8">
-        <f t="shared" si="32"/>
-        <v>22.346219999999988</v>
+        <v>26.589229999999986</v>
       </c>
       <c r="AB10" s="8">
         <f>AB5-AB6-AB7-AB8-AB9</f>
@@ -2113,60 +2111,60 @@
         <v>-269.29999999999984</v>
       </c>
       <c r="AF10" s="8">
-        <f t="shared" ref="AF10:AO10" si="33">AF5-AF6-AF7-AF8-AF9</f>
+        <f t="shared" ref="AF10:AO10" si="32">AF5-AF6-AF7-AF8-AF9</f>
         <v>-1871.9</v>
       </c>
       <c r="AG10" s="8">
+        <f t="shared" si="32"/>
+        <v>158.49999999999997</v>
+      </c>
+      <c r="AH10" s="8">
+        <f t="shared" si="32"/>
+        <v>133.19999999999999</v>
+      </c>
+      <c r="AI10" s="8">
+        <f t="shared" si="32"/>
+        <v>308.01655999999997</v>
+      </c>
+      <c r="AJ10" s="8">
+        <f t="shared" si="32"/>
+        <v>339.29912139999982</v>
+      </c>
+      <c r="AK10" s="8">
+        <f t="shared" si="32"/>
+        <v>357.37490663199981</v>
+      </c>
+      <c r="AL10" s="8">
+        <f t="shared" si="32"/>
+        <v>364.64876476464002</v>
+      </c>
+      <c r="AM10" s="8">
+        <f t="shared" si="32"/>
+        <v>378.78484786601268</v>
+      </c>
+      <c r="AN10" s="8">
+        <f t="shared" si="32"/>
+        <v>382.66651864467286</v>
+      </c>
+      <c r="AO10" s="8">
+        <f t="shared" si="32"/>
+        <v>386.57762390111941</v>
+      </c>
+      <c r="AP10" s="8">
+        <f t="shared" ref="AP10:AS10" si="33">AP5-AP6-AP7-AP8-AP9</f>
+        <v>390.51939620313055</v>
+      </c>
+      <c r="AQ10" s="8">
         <f t="shared" si="33"/>
-        <v>158.49999999999997</v>
-      </c>
-      <c r="AH10" s="8">
+        <v>394.4929866218618</v>
+      </c>
+      <c r="AR10" s="8">
         <f t="shared" si="33"/>
-        <v>133.19999999999999</v>
-      </c>
-      <c r="AI10" s="8">
+        <v>398.49947329911043</v>
+      </c>
+      <c r="AS10" s="8">
         <f t="shared" si="33"/>
-        <v>303.90079999999995</v>
-      </c>
-      <c r="AJ10" s="8">
-        <f t="shared" si="33"/>
-        <v>332.9205819999998</v>
-      </c>
-      <c r="AK10" s="8">
-        <f t="shared" si="33"/>
-        <v>350.75465415999975</v>
-      </c>
-      <c r="AL10" s="8">
-        <f t="shared" si="33"/>
-        <v>357.89610724319965</v>
-      </c>
-      <c r="AM10" s="8">
-        <f t="shared" si="33"/>
-        <v>371.89713719414374</v>
-      </c>
-      <c r="AN10" s="8">
-        <f t="shared" si="33"/>
-        <v>386.23410918216751</v>
-      </c>
-      <c r="AO10" s="8">
-        <f t="shared" si="33"/>
-        <v>390.18089034398906</v>
-      </c>
-      <c r="AP10" s="8">
-        <f t="shared" ref="AP10:AS10" si="34">AP5-AP6-AP7-AP8-AP9</f>
-        <v>394.15869531042881</v>
-      </c>
-      <c r="AQ10" s="8">
-        <f t="shared" si="34"/>
-        <v>398.16867872023323</v>
-      </c>
-      <c r="AR10" s="8">
-        <f t="shared" si="34"/>
-        <v>402.2119223184655</v>
-      </c>
-      <c r="AS10" s="8">
-        <f t="shared" si="34"/>
-        <v>406.28944267157709</v>
+        <v>402.53986916202854</v>
       </c>
     </row>
     <row r="11" spans="2:162" x14ac:dyDescent="0.3">
@@ -2241,7 +2239,7 @@
         <v>6.7</v>
       </c>
       <c r="Y11" s="5">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Z11" s="5">
         <v>0</v>
@@ -2272,47 +2270,47 @@
       </c>
       <c r="AI11" s="5">
         <f>SUM(W11:Z11)</f>
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AJ11" s="5">
-        <f t="shared" ref="AJ11:AS11" si="35">AI11*1.05</f>
-        <v>6.1950000000000003</v>
+        <f t="shared" ref="AJ11:AS11" si="34">AI11*1.05</f>
+        <v>6.8250000000000002</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" si="35"/>
-        <v>6.5047500000000005</v>
+        <f t="shared" si="34"/>
+        <v>7.1662500000000007</v>
       </c>
       <c r="AL11" s="5">
-        <f t="shared" si="35"/>
-        <v>6.8299875000000005</v>
+        <f t="shared" si="34"/>
+        <v>7.5245625000000009</v>
       </c>
       <c r="AM11" s="5">
-        <f t="shared" si="35"/>
-        <v>7.1714868750000011</v>
+        <f t="shared" si="34"/>
+        <v>7.9007906250000017</v>
       </c>
       <c r="AN11" s="5">
-        <f t="shared" si="35"/>
-        <v>7.5300612187500011</v>
+        <f t="shared" si="34"/>
+        <v>8.2958301562500019</v>
       </c>
       <c r="AO11" s="5">
-        <f t="shared" si="35"/>
-        <v>7.9065642796875011</v>
+        <f t="shared" si="34"/>
+        <v>8.7106216640625025</v>
       </c>
       <c r="AP11" s="5">
-        <f t="shared" si="35"/>
-        <v>8.3018924936718772</v>
+        <f t="shared" si="34"/>
+        <v>9.1461527472656279</v>
       </c>
       <c r="AQ11" s="5">
-        <f t="shared" si="35"/>
-        <v>8.7169871183554708</v>
+        <f t="shared" si="34"/>
+        <v>9.6034603846289102</v>
       </c>
       <c r="AR11" s="5">
-        <f t="shared" si="35"/>
-        <v>9.1528364742732453</v>
+        <f t="shared" si="34"/>
+        <v>10.083633403860356</v>
       </c>
       <c r="AS11" s="5">
-        <f t="shared" si="35"/>
-        <v>9.6104782979869086</v>
+        <f t="shared" si="34"/>
+        <v>10.587815074053374</v>
       </c>
     </row>
     <row r="12" spans="2:162" x14ac:dyDescent="0.3">
@@ -2387,7 +2385,7 @@
         <v>34.5</v>
       </c>
       <c r="Y12" s="5">
-        <v>33</v>
+        <v>34.1</v>
       </c>
       <c r="Z12" s="5">
         <v>33</v>
@@ -2418,47 +2416,47 @@
       </c>
       <c r="AI12" s="5">
         <f>SUM(W12:Z12)</f>
-        <v>134.19999999999999</v>
+        <v>135.30000000000001</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" ref="AJ12:AO12" si="36">AI12*0.8</f>
-        <v>107.36</v>
+        <f t="shared" ref="AJ12:AO12" si="35">AI12*0.8</f>
+        <v>108.24000000000001</v>
       </c>
       <c r="AK12" s="5">
-        <f t="shared" si="36"/>
-        <v>85.888000000000005</v>
+        <f t="shared" si="35"/>
+        <v>86.592000000000013</v>
       </c>
       <c r="AL12" s="5">
-        <f t="shared" si="36"/>
-        <v>68.710400000000007</v>
+        <f t="shared" si="35"/>
+        <v>69.273600000000016</v>
       </c>
       <c r="AM12" s="5">
-        <f t="shared" si="36"/>
-        <v>54.968320000000006</v>
+        <f t="shared" si="35"/>
+        <v>55.418880000000016</v>
       </c>
       <c r="AN12" s="5">
-        <f t="shared" si="36"/>
-        <v>43.97465600000001</v>
+        <f t="shared" si="35"/>
+        <v>44.335104000000015</v>
       </c>
       <c r="AO12" s="5">
-        <f t="shared" si="36"/>
-        <v>35.17972480000001</v>
+        <f t="shared" si="35"/>
+        <v>35.468083200000017</v>
       </c>
       <c r="AP12" s="5">
-        <f t="shared" ref="AP12" si="37">AO12*0.8</f>
-        <v>28.143779840000008</v>
+        <f t="shared" ref="AP12" si="36">AO12*0.8</f>
+        <v>28.374466560000016</v>
       </c>
       <c r="AQ12" s="5">
-        <f t="shared" ref="AQ12" si="38">AP12*0.8</f>
-        <v>22.515023872000008</v>
+        <f t="shared" ref="AQ12" si="37">AP12*0.8</f>
+        <v>22.699573248000014</v>
       </c>
       <c r="AR12" s="5">
-        <f t="shared" ref="AR12" si="39">AQ12*0.8</f>
-        <v>18.012019097600007</v>
+        <f t="shared" ref="AR12" si="38">AQ12*0.8</f>
+        <v>18.159658598400011</v>
       </c>
       <c r="AS12" s="5">
-        <f t="shared" ref="AS12" si="40">AR12*0.8</f>
-        <v>14.409615278080006</v>
+        <f t="shared" ref="AS12" si="39">AR12*0.8</f>
+        <v>14.52772687872001</v>
       </c>
     </row>
     <row r="13" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2466,100 +2464,100 @@
         <v>29</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:D13" si="41">C10-C11-C12</f>
+        <f t="shared" ref="C13:D13" si="40">C10-C11-C12</f>
         <v>-69.100000000000009</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>-18.499999999999993</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" ref="E13" si="42">E10-E11-E12</f>
+        <f t="shared" ref="E13" si="41">E10-E11-E12</f>
         <v>-53.1</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" ref="F13" si="43">F10-F11-F12</f>
+        <f t="shared" ref="F13" si="42">F10-F11-F12</f>
         <v>-23.999999999999996</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" ref="G13:H13" si="44">G10-G11-G12</f>
+        <f t="shared" ref="G13:H13" si="43">G10-G11-G12</f>
         <v>-66.600000000000023</v>
       </c>
       <c r="H13" s="8">
+        <f t="shared" si="43"/>
+        <v>23.400000000000006</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" ref="I13:J13" si="44">I10-I11-I12</f>
+        <v>-223.89999999999998</v>
+      </c>
+      <c r="J13" s="8">
         <f t="shared" si="44"/>
-        <v>23.400000000000006</v>
-      </c>
-      <c r="I13" s="8">
-        <f t="shared" ref="I13:J13" si="45">I10-I11-I12</f>
-        <v>-223.89999999999998</v>
-      </c>
-      <c r="J13" s="8">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" ref="K13:L13" si="45">K10-K11-K12</f>
+        <v>-1214.2</v>
+      </c>
+      <c r="L13" s="8">
         <f t="shared" si="45"/>
-        <v>71.599999999999994</v>
-      </c>
-      <c r="K13" s="8">
-        <f t="shared" ref="K13:L13" si="46">K10-K11-K12</f>
-        <v>-1214.2</v>
-      </c>
-      <c r="L13" s="8">
-        <f t="shared" si="46"/>
         <v>-675.39999999999986</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" ref="M13" si="47">M10-M11-M12</f>
+        <f t="shared" ref="M13" si="46">M10-M11-M12</f>
         <v>8.2999999999999829</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" ref="N13" si="48">N10-N11-N12</f>
+        <f t="shared" ref="N13" si="47">N10-N11-N12</f>
         <v>-33.399999999999977</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" ref="O13:P13" si="49">O10-O11-O12</f>
+        <f t="shared" ref="O13:P13" si="48">O10-O11-O12</f>
         <v>0</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>4.8000000000000185</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" ref="Q13" si="50">Q10-Q11-Q12</f>
+        <f t="shared" ref="Q13" si="49">Q10-Q11-Q12</f>
         <v>14.499999999999993</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" ref="R13" si="51">R10-R11-R12</f>
+        <f t="shared" ref="R13" si="50">R10-R11-R12</f>
         <v>1.2000000000000028</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" ref="S13:V13" si="52">S10-S11-S12</f>
+        <f t="shared" ref="S13:V13" si="51">S10-S11-S12</f>
         <v>10.199999999999967</v>
       </c>
       <c r="T13" s="8">
+        <f t="shared" si="51"/>
+        <v>3.7999999999999758</v>
+      </c>
+      <c r="U13" s="8">
+        <f t="shared" si="51"/>
+        <v>-15.799999999999972</v>
+      </c>
+      <c r="V13" s="8">
+        <f t="shared" si="51"/>
+        <v>15.699999999999918</v>
+      </c>
+      <c r="W13" s="8">
+        <f t="shared" ref="W13:Z13" si="52">W10-W11-W12</f>
+        <v>-22.7</v>
+      </c>
+      <c r="X13" s="8">
         <f t="shared" si="52"/>
-        <v>3.7999999999999758</v>
-      </c>
-      <c r="U13" s="8">
+        <v>-20.500000000000004</v>
+      </c>
+      <c r="Y13" s="8">
         <f t="shared" si="52"/>
-        <v>-15.799999999999972</v>
-      </c>
-      <c r="V13" s="8">
+        <v>4.3000000000000185</v>
+      </c>
+      <c r="Z13" s="8">
         <f t="shared" si="52"/>
-        <v>15.699999999999918</v>
-      </c>
-      <c r="W13" s="8">
-        <f t="shared" ref="W13:Z13" si="53">W10-W11-W12</f>
-        <v>-22.7</v>
-      </c>
-      <c r="X13" s="8">
-        <f t="shared" si="53"/>
-        <v>-20.500000000000004</v>
-      </c>
-      <c r="Y13" s="8">
-        <f t="shared" si="53"/>
-        <v>-10.977619999999973</v>
-      </c>
-      <c r="Z13" s="8">
-        <f t="shared" si="53"/>
-        <v>-10.653780000000012</v>
+        <v>-6.4107700000000136</v>
       </c>
       <c r="AB13" s="8">
         <f>AB10-AB11-AB12</f>
@@ -2578,60 +2576,60 @@
         <v>-195.49999999999986</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" ref="AF13:AO13" si="54">AF10-AF11-AF12</f>
+        <f t="shared" ref="AF13:AO13" si="53">AF10-AF11-AF12</f>
         <v>-1914.7</v>
       </c>
       <c r="AG13" s="8">
+        <f t="shared" si="53"/>
+        <v>20.499999999999972</v>
+      </c>
+      <c r="AH13" s="8">
+        <f t="shared" si="53"/>
+        <v>13.899999999999977</v>
+      </c>
+      <c r="AI13" s="8">
+        <f t="shared" si="53"/>
+        <v>166.21655999999996</v>
+      </c>
+      <c r="AJ13" s="8">
+        <f t="shared" si="53"/>
+        <v>224.23412139999982</v>
+      </c>
+      <c r="AK13" s="8">
+        <f t="shared" si="53"/>
+        <v>263.61665663199983</v>
+      </c>
+      <c r="AL13" s="8">
+        <f t="shared" si="53"/>
+        <v>287.85060226463997</v>
+      </c>
+      <c r="AM13" s="8">
+        <f t="shared" si="53"/>
+        <v>315.46517724101267</v>
+      </c>
+      <c r="AN13" s="8">
+        <f t="shared" si="53"/>
+        <v>330.03558448842284</v>
+      </c>
+      <c r="AO13" s="8">
+        <f t="shared" si="53"/>
+        <v>342.39891903705688</v>
+      </c>
+      <c r="AP13" s="8">
+        <f t="shared" ref="AP13:AS13" si="54">AP10-AP11-AP12</f>
+        <v>352.99877689586492</v>
+      </c>
+      <c r="AQ13" s="8">
         <f t="shared" si="54"/>
-        <v>20.499999999999972</v>
-      </c>
-      <c r="AH13" s="8">
+        <v>362.18995298923284</v>
+      </c>
+      <c r="AR13" s="8">
         <f t="shared" si="54"/>
-        <v>13.899999999999977</v>
-      </c>
-      <c r="AI13" s="8">
+        <v>370.25618129685006</v>
+      </c>
+      <c r="AS13" s="8">
         <f t="shared" si="54"/>
-        <v>163.80079999999998</v>
-      </c>
-      <c r="AJ13" s="8">
-        <f t="shared" si="54"/>
-        <v>219.36558199999979</v>
-      </c>
-      <c r="AK13" s="8">
-        <f t="shared" si="54"/>
-        <v>258.36190415999977</v>
-      </c>
-      <c r="AL13" s="8">
-        <f t="shared" si="54"/>
-        <v>282.35571974319964</v>
-      </c>
-      <c r="AM13" s="8">
-        <f t="shared" si="54"/>
-        <v>309.7573303191437</v>
-      </c>
-      <c r="AN13" s="8">
-        <f t="shared" si="54"/>
-        <v>334.72939196341747</v>
-      </c>
-      <c r="AO13" s="8">
-        <f t="shared" si="54"/>
-        <v>347.09460126430156</v>
-      </c>
-      <c r="AP13" s="8">
-        <f t="shared" ref="AP13:AS13" si="55">AP10-AP11-AP12</f>
-        <v>357.71302297675697</v>
-      </c>
-      <c r="AQ13" s="8">
-        <f t="shared" si="55"/>
-        <v>366.93666772987774</v>
-      </c>
-      <c r="AR13" s="8">
-        <f t="shared" si="55"/>
-        <v>375.04706674659224</v>
-      </c>
-      <c r="AS13" s="8">
-        <f t="shared" si="55"/>
-        <v>382.26934909551017</v>
+        <v>377.42432720925518</v>
       </c>
     </row>
     <row r="14" spans="2:162" x14ac:dyDescent="0.3">
@@ -2706,12 +2704,11 @@
         <v>29.4</v>
       </c>
       <c r="Y14" s="5">
-        <f t="shared" ref="Y14:Z14" si="56">Y13*0.05</f>
-        <v>-0.54888099999999873</v>
+        <v>91.9</v>
       </c>
       <c r="Z14" s="5">
-        <f t="shared" si="56"/>
-        <v>-0.53268900000000063</v>
+        <f t="shared" ref="Y14:Z14" si="55">Z13*0.05</f>
+        <v>-0.32053850000000073</v>
       </c>
       <c r="AB14" s="5">
         <v>5.6</v>
@@ -2739,47 +2736,47 @@
       </c>
       <c r="AI14" s="5">
         <f>SUM(W14:Z14)</f>
-        <v>25.218429999999998</v>
+        <v>117.87946150000001</v>
       </c>
       <c r="AJ14" s="5">
         <f>AJ13*0.2</f>
-        <v>43.873116399999958</v>
+        <v>44.846824279999964</v>
       </c>
       <c r="AK14" s="5">
-        <f t="shared" ref="AK14:AS14" si="57">AK13*0.2</f>
-        <v>51.672380831999959</v>
+        <f t="shared" ref="AK14:AS14" si="56">AK13*0.2</f>
+        <v>52.723331326399972</v>
       </c>
       <c r="AL14" s="5">
-        <f t="shared" si="57"/>
-        <v>56.471143948639934</v>
+        <f t="shared" si="56"/>
+        <v>57.570120452927995</v>
       </c>
       <c r="AM14" s="5">
-        <f t="shared" si="57"/>
-        <v>61.951466063828747</v>
+        <f t="shared" si="56"/>
+        <v>63.093035448202535</v>
       </c>
       <c r="AN14" s="5">
-        <f t="shared" si="57"/>
-        <v>66.945878392683497</v>
+        <f t="shared" si="56"/>
+        <v>66.007116897684568</v>
       </c>
       <c r="AO14" s="5">
-        <f t="shared" si="57"/>
-        <v>69.418920252860318</v>
+        <f t="shared" si="56"/>
+        <v>68.47978380741138</v>
       </c>
       <c r="AP14" s="5">
-        <f t="shared" si="57"/>
-        <v>71.542604595351392</v>
+        <f t="shared" si="56"/>
+        <v>70.59975537917299</v>
       </c>
       <c r="AQ14" s="5">
-        <f t="shared" si="57"/>
-        <v>73.387333545975551</v>
+        <f t="shared" si="56"/>
+        <v>72.437990597846564</v>
       </c>
       <c r="AR14" s="5">
-        <f t="shared" si="57"/>
-        <v>75.00941334931845</v>
+        <f t="shared" si="56"/>
+        <v>74.051236259370015</v>
       </c>
       <c r="AS14" s="5">
-        <f t="shared" si="57"/>
-        <v>76.453869819102039</v>
+        <f t="shared" si="56"/>
+        <v>75.484865441851042</v>
       </c>
     </row>
     <row r="15" spans="2:162" x14ac:dyDescent="0.3">
@@ -2923,100 +2920,100 @@
         <v>32</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:D16" si="58">C13-C14-C15</f>
+        <f t="shared" ref="C16:D16" si="57">C13-C14-C15</f>
         <v>-51.20000000000001</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-15.899999999999993</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" ref="E16" si="59">E13-E14-E15</f>
+        <f t="shared" ref="E16" si="58">E13-E14-E15</f>
         <v>-38.299999999999997</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" ref="F16" si="60">F13-F14-F15</f>
+        <f t="shared" ref="F16" si="59">F13-F14-F15</f>
         <v>-3.2999999999999949</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" ref="G16:H16" si="61">G13-G14-G15</f>
+        <f t="shared" ref="G16:H16" si="60">G13-G14-G15</f>
         <v>-60.800000000000026</v>
       </c>
       <c r="H16" s="8">
+        <f t="shared" si="60"/>
+        <v>6.5000000000000062</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" ref="I16:J16" si="61">I13-I14-I15</f>
+        <v>-147.09999999999997</v>
+      </c>
+      <c r="J16" s="8">
         <f t="shared" si="61"/>
-        <v>6.5000000000000062</v>
-      </c>
-      <c r="I16" s="8">
-        <f t="shared" ref="I16:J16" si="62">I13-I14-I15</f>
-        <v>-147.09999999999997</v>
-      </c>
-      <c r="J16" s="8">
+        <v>90.399999999999991</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" ref="K16:L16" si="62">K13-K14-K15</f>
+        <v>-1171.2</v>
+      </c>
+      <c r="L16" s="8">
         <f t="shared" si="62"/>
-        <v>90.399999999999991</v>
-      </c>
-      <c r="K16" s="8">
-        <f t="shared" ref="K16:L16" si="63">K13-K14-K15</f>
-        <v>-1171.2</v>
-      </c>
-      <c r="L16" s="8">
-        <f t="shared" si="63"/>
         <v>-691.99999999999989</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" ref="M16" si="64">M13-M14-M15</f>
+        <f t="shared" ref="M16" si="63">M13-M14-M15</f>
         <v>0.99999999999998312</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" ref="N16" si="65">N13-N14-N15</f>
+        <f t="shared" ref="N16" si="64">N13-N14-N15</f>
         <v>-33.199999999999974</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" ref="O16:P16" si="66">O13-O14-O15</f>
+        <f t="shared" ref="O16:P16" si="65">O13-O14-O15</f>
         <v>-3.9</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>-1.7999999999999812</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" ref="Q16" si="67">Q13-Q14-Q15</f>
+        <f t="shared" ref="Q16" si="66">Q13-Q14-Q15</f>
         <v>-2.5000000000000071</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" ref="R16" si="68">R13-R14-R15</f>
+        <f t="shared" ref="R16" si="67">R13-R14-R15</f>
         <v>-12.199999999999998</v>
       </c>
       <c r="S16" s="8">
-        <f t="shared" ref="S16:V16" si="69">S13-S14-S15</f>
+        <f t="shared" ref="S16:V16" si="68">S13-S14-S15</f>
         <v>2.8999999999999675</v>
       </c>
       <c r="T16" s="8">
+        <f t="shared" si="68"/>
+        <v>-1.4000000000000243</v>
+      </c>
+      <c r="U16" s="8">
+        <f t="shared" si="68"/>
+        <v>-12.899999999999972</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" si="68"/>
+        <v>33.39999999999992</v>
+      </c>
+      <c r="W16" s="8">
+        <f t="shared" ref="W16:Z16" si="69">W13-W14-W15</f>
+        <v>-19.599999999999998</v>
+      </c>
+      <c r="X16" s="8">
         <f t="shared" si="69"/>
-        <v>-1.4000000000000243</v>
-      </c>
-      <c r="U16" s="8">
+        <v>-49.900000000000006</v>
+      </c>
+      <c r="Y16" s="8">
         <f t="shared" si="69"/>
-        <v>-12.899999999999972</v>
-      </c>
-      <c r="V16" s="8">
+        <v>-87.6</v>
+      </c>
+      <c r="Z16" s="8">
         <f t="shared" si="69"/>
-        <v>33.39999999999992</v>
-      </c>
-      <c r="W16" s="8">
-        <f t="shared" ref="W16:Z16" si="70">W13-W14-W15</f>
-        <v>-19.599999999999998</v>
-      </c>
-      <c r="X16" s="8">
-        <f t="shared" si="70"/>
-        <v>-49.900000000000006</v>
-      </c>
-      <c r="Y16" s="8">
-        <f t="shared" si="70"/>
-        <v>-10.428738999999975</v>
-      </c>
-      <c r="Z16" s="8">
-        <f t="shared" si="70"/>
-        <v>-10.12109100000001</v>
+        <v>-6.0902315000000131</v>
       </c>
       <c r="AB16" s="8">
         <f>AB13-AB14-AB15</f>
@@ -3039,524 +3036,524 @@
         <v>-1895.4</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" ref="AG16:AO16" si="71">AG13-AG14-AG15</f>
+        <f t="shared" ref="AG16:AO16" si="70">AG13-AG14-AG15</f>
         <v>-20.400000000000027</v>
       </c>
       <c r="AH16" s="8">
+        <f t="shared" si="70"/>
+        <v>21.999999999999979</v>
+      </c>
+      <c r="AI16" s="8">
+        <f t="shared" si="70"/>
+        <v>48.337098499999954</v>
+      </c>
+      <c r="AJ16" s="8">
+        <f t="shared" si="70"/>
+        <v>179.38729711999986</v>
+      </c>
+      <c r="AK16" s="8">
+        <f t="shared" si="70"/>
+        <v>210.89332530559986</v>
+      </c>
+      <c r="AL16" s="8">
+        <f t="shared" si="70"/>
+        <v>230.28048181171198</v>
+      </c>
+      <c r="AM16" s="8">
+        <f t="shared" si="70"/>
+        <v>252.37214179281014</v>
+      </c>
+      <c r="AN16" s="8">
+        <f t="shared" si="70"/>
+        <v>264.02846759073827</v>
+      </c>
+      <c r="AO16" s="8">
+        <f t="shared" si="70"/>
+        <v>273.91913522964552</v>
+      </c>
+      <c r="AP16" s="8">
+        <f t="shared" ref="AP16:AS16" si="71">AP13-AP14-AP15</f>
+        <v>282.39902151669196</v>
+      </c>
+      <c r="AQ16" s="8">
         <f t="shared" si="71"/>
-        <v>21.999999999999979</v>
-      </c>
-      <c r="AI16" s="8">
+        <v>289.75196239138626</v>
+      </c>
+      <c r="AR16" s="8">
         <f t="shared" si="71"/>
-        <v>138.58236999999997</v>
-      </c>
-      <c r="AJ16" s="8">
+        <v>296.20494503748006</v>
+      </c>
+      <c r="AS16" s="8">
         <f t="shared" si="71"/>
-        <v>175.49246559999983</v>
-      </c>
-      <c r="AK16" s="8">
-        <f t="shared" si="71"/>
-        <v>206.68952332799981</v>
-      </c>
-      <c r="AL16" s="8">
-        <f t="shared" si="71"/>
-        <v>225.88457579455971</v>
-      </c>
-      <c r="AM16" s="8">
-        <f t="shared" si="71"/>
-        <v>247.80586425531496</v>
-      </c>
-      <c r="AN16" s="8">
-        <f t="shared" si="71"/>
-        <v>267.78351357073399</v>
-      </c>
-      <c r="AO16" s="8">
-        <f t="shared" si="71"/>
-        <v>277.67568101144127</v>
-      </c>
-      <c r="AP16" s="8">
-        <f t="shared" ref="AP16:AS16" si="72">AP13-AP14-AP15</f>
-        <v>286.17041838140557</v>
-      </c>
-      <c r="AQ16" s="8">
-        <f t="shared" si="72"/>
-        <v>293.5493341839022</v>
-      </c>
-      <c r="AR16" s="8">
-        <f t="shared" si="72"/>
-        <v>300.0376533972738</v>
-      </c>
-      <c r="AS16" s="8">
-        <f t="shared" si="72"/>
-        <v>305.81547927640815</v>
+        <v>301.93946176740417</v>
       </c>
       <c r="AT16" s="1">
         <f>AS16*(1+$AV$21)</f>
-        <v>302.75732448364408</v>
+        <v>298.92006714973013</v>
       </c>
       <c r="AU16" s="1">
-        <f t="shared" ref="AU16:DF16" si="73">AT16*(1+$AV$21)</f>
-        <v>299.72975123880764</v>
+        <f t="shared" ref="AU16:DF16" si="72">AT16*(1+$AV$21)</f>
+        <v>295.93086647823282</v>
       </c>
       <c r="AV16" s="1">
+        <f t="shared" si="72"/>
+        <v>292.97155781345049</v>
+      </c>
+      <c r="AW16" s="1">
+        <f t="shared" si="72"/>
+        <v>290.04184223531598</v>
+      </c>
+      <c r="AX16" s="1">
+        <f t="shared" si="72"/>
+        <v>287.14142381296284</v>
+      </c>
+      <c r="AY16" s="1">
+        <f t="shared" si="72"/>
+        <v>284.27000957483324</v>
+      </c>
+      <c r="AZ16" s="1">
+        <f t="shared" si="72"/>
+        <v>281.4273094790849</v>
+      </c>
+      <c r="BA16" s="1">
+        <f t="shared" si="72"/>
+        <v>278.61303638429405</v>
+      </c>
+      <c r="BB16" s="1">
+        <f t="shared" si="72"/>
+        <v>275.82690602045113</v>
+      </c>
+      <c r="BC16" s="1">
+        <f t="shared" si="72"/>
+        <v>273.06863696024664</v>
+      </c>
+      <c r="BD16" s="1">
+        <f t="shared" si="72"/>
+        <v>270.33795059064414</v>
+      </c>
+      <c r="BE16" s="1">
+        <f t="shared" si="72"/>
+        <v>267.63457108473767</v>
+      </c>
+      <c r="BF16" s="1">
+        <f t="shared" si="72"/>
+        <v>264.95822537389029</v>
+      </c>
+      <c r="BG16" s="1">
+        <f t="shared" si="72"/>
+        <v>262.30864312015137</v>
+      </c>
+      <c r="BH16" s="1">
+        <f t="shared" si="72"/>
+        <v>259.68555668894987</v>
+      </c>
+      <c r="BI16" s="1">
+        <f t="shared" si="72"/>
+        <v>257.0887011220604</v>
+      </c>
+      <c r="BJ16" s="1">
+        <f t="shared" si="72"/>
+        <v>254.51781411083979</v>
+      </c>
+      <c r="BK16" s="1">
+        <f t="shared" si="72"/>
+        <v>251.97263596973139</v>
+      </c>
+      <c r="BL16" s="1">
+        <f t="shared" si="72"/>
+        <v>249.45290961003406</v>
+      </c>
+      <c r="BM16" s="1">
+        <f t="shared" si="72"/>
+        <v>246.95838051393372</v>
+      </c>
+      <c r="BN16" s="1">
+        <f t="shared" si="72"/>
+        <v>244.48879670879438</v>
+      </c>
+      <c r="BO16" s="1">
+        <f t="shared" si="72"/>
+        <v>242.04390874170645</v>
+      </c>
+      <c r="BP16" s="1">
+        <f t="shared" si="72"/>
+        <v>239.62346965428938</v>
+      </c>
+      <c r="BQ16" s="1">
+        <f t="shared" si="72"/>
+        <v>237.22723495774648</v>
+      </c>
+      <c r="BR16" s="1">
+        <f t="shared" si="72"/>
+        <v>234.85496260816902</v>
+      </c>
+      <c r="BS16" s="1">
+        <f t="shared" si="72"/>
+        <v>232.50641298208731</v>
+      </c>
+      <c r="BT16" s="1">
+        <f t="shared" si="72"/>
+        <v>230.18134885226644</v>
+      </c>
+      <c r="BU16" s="1">
+        <f t="shared" si="72"/>
+        <v>227.87953536374377</v>
+      </c>
+      <c r="BV16" s="1">
+        <f t="shared" si="72"/>
+        <v>225.60074001010634</v>
+      </c>
+      <c r="BW16" s="1">
+        <f t="shared" si="72"/>
+        <v>223.34473261000528</v>
+      </c>
+      <c r="BX16" s="1">
+        <f t="shared" si="72"/>
+        <v>221.11128528390523</v>
+      </c>
+      <c r="BY16" s="1">
+        <f t="shared" si="72"/>
+        <v>218.90017243106618</v>
+      </c>
+      <c r="BZ16" s="1">
+        <f t="shared" si="72"/>
+        <v>216.71117070675552</v>
+      </c>
+      <c r="CA16" s="1">
+        <f t="shared" si="72"/>
+        <v>214.54405899968796</v>
+      </c>
+      <c r="CB16" s="1">
+        <f t="shared" si="72"/>
+        <v>212.39861840969107</v>
+      </c>
+      <c r="CC16" s="1">
+        <f t="shared" si="72"/>
+        <v>210.27463222559416</v>
+      </c>
+      <c r="CD16" s="1">
+        <f t="shared" si="72"/>
+        <v>208.17188590333822</v>
+      </c>
+      <c r="CE16" s="1">
+        <f t="shared" si="72"/>
+        <v>206.09016704430485</v>
+      </c>
+      <c r="CF16" s="1">
+        <f t="shared" si="72"/>
+        <v>204.02926537386179</v>
+      </c>
+      <c r="CG16" s="1">
+        <f t="shared" si="72"/>
+        <v>201.98897272012317</v>
+      </c>
+      <c r="CH16" s="1">
+        <f t="shared" si="72"/>
+        <v>199.96908299292193</v>
+      </c>
+      <c r="CI16" s="1">
+        <f t="shared" si="72"/>
+        <v>197.9693921629927</v>
+      </c>
+      <c r="CJ16" s="1">
+        <f t="shared" si="72"/>
+        <v>195.98969824136279</v>
+      </c>
+      <c r="CK16" s="1">
+        <f t="shared" si="72"/>
+        <v>194.02980125894916</v>
+      </c>
+      <c r="CL16" s="1">
+        <f t="shared" si="72"/>
+        <v>192.08950324635967</v>
+      </c>
+      <c r="CM16" s="1">
+        <f t="shared" si="72"/>
+        <v>190.16860821389608</v>
+      </c>
+      <c r="CN16" s="1">
+        <f t="shared" si="72"/>
+        <v>188.26692213175713</v>
+      </c>
+      <c r="CO16" s="1">
+        <f t="shared" si="72"/>
+        <v>186.38425291043956</v>
+      </c>
+      <c r="CP16" s="1">
+        <f t="shared" si="72"/>
+        <v>184.52041038133515</v>
+      </c>
+      <c r="CQ16" s="1">
+        <f t="shared" si="72"/>
+        <v>182.6752062775218</v>
+      </c>
+      <c r="CR16" s="1">
+        <f t="shared" si="72"/>
+        <v>180.84845421474657</v>
+      </c>
+      <c r="CS16" s="1">
+        <f t="shared" si="72"/>
+        <v>179.03996967259911</v>
+      </c>
+      <c r="CT16" s="1">
+        <f t="shared" si="72"/>
+        <v>177.24956997587313</v>
+      </c>
+      <c r="CU16" s="1">
+        <f t="shared" si="72"/>
+        <v>175.47707427611439</v>
+      </c>
+      <c r="CV16" s="1">
+        <f t="shared" si="72"/>
+        <v>173.72230353335326</v>
+      </c>
+      <c r="CW16" s="1">
+        <f t="shared" si="72"/>
+        <v>171.98508049801973</v>
+      </c>
+      <c r="CX16" s="1">
+        <f t="shared" si="72"/>
+        <v>170.26522969303952</v>
+      </c>
+      <c r="CY16" s="1">
+        <f t="shared" si="72"/>
+        <v>168.56257739610911</v>
+      </c>
+      <c r="CZ16" s="1">
+        <f t="shared" si="72"/>
+        <v>166.876951622148</v>
+      </c>
+      <c r="DA16" s="1">
+        <f t="shared" si="72"/>
+        <v>165.20818210592651</v>
+      </c>
+      <c r="DB16" s="1">
+        <f t="shared" si="72"/>
+        <v>163.55610028486726</v>
+      </c>
+      <c r="DC16" s="1">
+        <f t="shared" si="72"/>
+        <v>161.92053928201858</v>
+      </c>
+      <c r="DD16" s="1">
+        <f t="shared" si="72"/>
+        <v>160.30133388919839</v>
+      </c>
+      <c r="DE16" s="1">
+        <f t="shared" si="72"/>
+        <v>158.69832055030639</v>
+      </c>
+      <c r="DF16" s="1">
+        <f t="shared" si="72"/>
+        <v>157.11133734480333</v>
+      </c>
+      <c r="DG16" s="1">
+        <f t="shared" ref="DG16:FF16" si="73">DF16*(1+$AV$21)</f>
+        <v>155.54022397135529</v>
+      </c>
+      <c r="DH16" s="1">
         <f t="shared" si="73"/>
-        <v>296.73245372641958</v>
-      </c>
-      <c r="AW16" s="1">
+        <v>153.98482173164174</v>
+      </c>
+      <c r="DI16" s="1">
         <f t="shared" si="73"/>
-        <v>293.7651291891554</v>
-      </c>
-      <c r="AX16" s="1">
+        <v>152.44497351432531</v>
+      </c>
+      <c r="DJ16" s="1">
         <f t="shared" si="73"/>
-        <v>290.82747789726386</v>
-      </c>
-      <c r="AY16" s="1">
+        <v>150.92052377918205</v>
+      </c>
+      <c r="DK16" s="1">
         <f t="shared" si="73"/>
-        <v>287.91920311829119</v>
-      </c>
-      <c r="AZ16" s="1">
+        <v>149.41131854139022</v>
+      </c>
+      <c r="DL16" s="1">
         <f t="shared" si="73"/>
-        <v>285.04001108710827</v>
-      </c>
-      <c r="BA16" s="1">
+        <v>147.91720535597631</v>
+      </c>
+      <c r="DM16" s="1">
         <f t="shared" si="73"/>
-        <v>282.18961097623719</v>
-      </c>
-      <c r="BB16" s="1">
+        <v>146.43803330241656</v>
+      </c>
+      <c r="DN16" s="1">
         <f t="shared" si="73"/>
-        <v>279.36771486647484</v>
-      </c>
-      <c r="BC16" s="1">
+        <v>144.97365296939239</v>
+      </c>
+      <c r="DO16" s="1">
         <f t="shared" si="73"/>
-        <v>276.57403771781009</v>
-      </c>
-      <c r="BD16" s="1">
+        <v>143.52391643969847</v>
+      </c>
+      <c r="DP16" s="1">
         <f t="shared" si="73"/>
-        <v>273.80829734063201</v>
-      </c>
-      <c r="BE16" s="1">
+        <v>142.08867727530148</v>
+      </c>
+      <c r="DQ16" s="1">
         <f t="shared" si="73"/>
-        <v>271.07021436722567</v>
-      </c>
-      <c r="BF16" s="1">
+        <v>140.66779050254846</v>
+      </c>
+      <c r="DR16" s="1">
         <f t="shared" si="73"/>
-        <v>268.35951222355339</v>
-      </c>
-      <c r="BG16" s="1">
+        <v>139.26111259752298</v>
+      </c>
+      <c r="DS16" s="1">
         <f t="shared" si="73"/>
-        <v>265.67591710131785</v>
-      </c>
-      <c r="BH16" s="1">
+        <v>137.86850147154775</v>
+      </c>
+      <c r="DT16" s="1">
         <f t="shared" si="73"/>
-        <v>263.01915793030469</v>
-      </c>
-      <c r="BI16" s="1">
+        <v>136.48981645683227</v>
+      </c>
+      <c r="DU16" s="1">
         <f t="shared" si="73"/>
-        <v>260.38896635100161</v>
-      </c>
-      <c r="BJ16" s="1">
+        <v>135.12491829226394</v>
+      </c>
+      <c r="DV16" s="1">
         <f t="shared" si="73"/>
-        <v>257.7850766874916</v>
-      </c>
-      <c r="BK16" s="1">
+        <v>133.77366910934131</v>
+      </c>
+      <c r="DW16" s="1">
         <f t="shared" si="73"/>
-        <v>255.20722592061668</v>
-      </c>
-      <c r="BL16" s="1">
+        <v>132.43593241824789</v>
+      </c>
+      <c r="DX16" s="1">
         <f t="shared" si="73"/>
-        <v>252.65515366141051</v>
-      </c>
-      <c r="BM16" s="1">
+        <v>131.11157309406542</v>
+      </c>
+      <c r="DY16" s="1">
         <f t="shared" si="73"/>
-        <v>250.1286021247964</v>
-      </c>
-      <c r="BN16" s="1">
+        <v>129.80045736312476</v>
+      </c>
+      <c r="DZ16" s="1">
         <f t="shared" si="73"/>
-        <v>247.62731610354842</v>
-      </c>
-      <c r="BO16" s="1">
+        <v>128.5024527894935</v>
+      </c>
+      <c r="EA16" s="1">
         <f t="shared" si="73"/>
-        <v>245.15104294251293</v>
-      </c>
-      <c r="BP16" s="1">
+        <v>127.21742826159857</v>
+      </c>
+      <c r="EB16" s="1">
         <f t="shared" si="73"/>
-        <v>242.6995325130878</v>
-      </c>
-      <c r="BQ16" s="1">
+        <v>125.94525397898258</v>
+      </c>
+      <c r="EC16" s="1">
         <f t="shared" si="73"/>
-        <v>240.27253718795691</v>
-      </c>
-      <c r="BR16" s="1">
+        <v>124.68580143919274</v>
+      </c>
+      <c r="ED16" s="1">
         <f t="shared" si="73"/>
-        <v>237.86981181607734</v>
-      </c>
-      <c r="BS16" s="1">
+        <v>123.43894342480081</v>
+      </c>
+      <c r="EE16" s="1">
         <f t="shared" si="73"/>
-        <v>235.49111369791657</v>
-      </c>
-      <c r="BT16" s="1">
+        <v>122.2045539905528</v>
+      </c>
+      <c r="EF16" s="1">
         <f t="shared" si="73"/>
-        <v>233.13620256093742</v>
-      </c>
-      <c r="BU16" s="1">
+        <v>120.98250845064727</v>
+      </c>
+      <c r="EG16" s="1">
         <f t="shared" si="73"/>
-        <v>230.80484053532805</v>
-      </c>
-      <c r="BV16" s="1">
+        <v>119.7726833661408</v>
+      </c>
+      <c r="EH16" s="1">
         <f t="shared" si="73"/>
-        <v>228.49679212997478</v>
-      </c>
-      <c r="BW16" s="1">
+        <v>118.57495653247939</v>
+      </c>
+      <c r="EI16" s="1">
         <f t="shared" si="73"/>
-        <v>226.21182420867504</v>
-      </c>
-      <c r="BX16" s="1">
+        <v>117.38920696715459</v>
+      </c>
+      <c r="EJ16" s="1">
         <f t="shared" si="73"/>
-        <v>223.94970596658828</v>
-      </c>
-      <c r="BY16" s="1">
+        <v>116.21531489748304</v>
+      </c>
+      <c r="EK16" s="1">
         <f t="shared" si="73"/>
-        <v>221.71020890692239</v>
-      </c>
-      <c r="BZ16" s="1">
+        <v>115.0531617485082</v>
+      </c>
+      <c r="EL16" s="1">
         <f t="shared" si="73"/>
-        <v>219.49310681785317</v>
-      </c>
-      <c r="CA16" s="1">
+        <v>113.90263013102312</v>
+      </c>
+      <c r="EM16" s="1">
         <f t="shared" si="73"/>
-        <v>217.29817574967464</v>
-      </c>
-      <c r="CB16" s="1">
+        <v>112.76360382971288</v>
+      </c>
+      <c r="EN16" s="1">
         <f t="shared" si="73"/>
-        <v>215.12519399217788</v>
-      </c>
-      <c r="CC16" s="1">
+        <v>111.63596779141575</v>
+      </c>
+      <c r="EO16" s="1">
         <f t="shared" si="73"/>
-        <v>212.97394205225609</v>
-      </c>
-      <c r="CD16" s="1">
+        <v>110.51960811350159</v>
+      </c>
+      <c r="EP16" s="1">
         <f t="shared" si="73"/>
-        <v>210.84420263173354</v>
-      </c>
-      <c r="CE16" s="1">
+        <v>109.41441203236657</v>
+      </c>
+      <c r="EQ16" s="1">
         <f t="shared" si="73"/>
-        <v>208.7357606054162</v>
-      </c>
-      <c r="CF16" s="1">
+        <v>108.32026791204291</v>
+      </c>
+      <c r="ER16" s="1">
         <f t="shared" si="73"/>
-        <v>206.64840299936205</v>
-      </c>
-      <c r="CG16" s="1">
+        <v>107.23706523292248</v>
+      </c>
+      <c r="ES16" s="1">
         <f t="shared" si="73"/>
-        <v>204.58191896936842</v>
-      </c>
-      <c r="CH16" s="1">
+        <v>106.16469458059325</v>
+      </c>
+      <c r="ET16" s="1">
         <f t="shared" si="73"/>
-        <v>202.53609977967474</v>
-      </c>
-      <c r="CI16" s="1">
+        <v>105.10304763478732</v>
+      </c>
+      <c r="EU16" s="1">
         <f t="shared" si="73"/>
-        <v>200.51073878187799</v>
-      </c>
-      <c r="CJ16" s="1">
+        <v>104.05201715843944</v>
+      </c>
+      <c r="EV16" s="1">
         <f t="shared" si="73"/>
-        <v>198.50563139405921</v>
-      </c>
-      <c r="CK16" s="1">
+        <v>103.01149698685505</v>
+      </c>
+      <c r="EW16" s="1">
         <f t="shared" si="73"/>
-        <v>196.52057508011862</v>
-      </c>
-      <c r="CL16" s="1">
+        <v>101.9813820169865</v>
+      </c>
+      <c r="EX16" s="1">
         <f t="shared" si="73"/>
-        <v>194.55536932931744</v>
-      </c>
-      <c r="CM16" s="1">
+        <v>100.96156819681663</v>
+      </c>
+      <c r="EY16" s="1">
         <f t="shared" si="73"/>
-        <v>192.60981563602428</v>
-      </c>
-      <c r="CN16" s="1">
+        <v>99.951952514848458</v>
+      </c>
+      <c r="EZ16" s="1">
         <f t="shared" si="73"/>
-        <v>190.68371747966404</v>
-      </c>
-      <c r="CO16" s="1">
+        <v>98.952432989699972</v>
+      </c>
+      <c r="FA16" s="1">
         <f t="shared" si="73"/>
-        <v>188.7768803048674</v>
-      </c>
-      <c r="CP16" s="1">
+        <v>97.962908659802977</v>
+      </c>
+      <c r="FB16" s="1">
         <f t="shared" si="73"/>
-        <v>186.88911150181872</v>
-      </c>
-      <c r="CQ16" s="1">
+        <v>96.983279573204953</v>
+      </c>
+      <c r="FC16" s="1">
         <f t="shared" si="73"/>
-        <v>185.02022038680053</v>
-      </c>
-      <c r="CR16" s="1">
+        <v>96.013446777472907</v>
+      </c>
+      <c r="FD16" s="1">
         <f t="shared" si="73"/>
-        <v>183.17001818293252</v>
-      </c>
-      <c r="CS16" s="1">
+        <v>95.053312309698171</v>
+      </c>
+      <c r="FE16" s="1">
         <f t="shared" si="73"/>
-        <v>181.3383180011032</v>
-      </c>
-      <c r="CT16" s="1">
+        <v>94.102779186601182</v>
+      </c>
+      <c r="FF16" s="1">
         <f t="shared" si="73"/>
-        <v>179.52493482109216</v>
-      </c>
-      <c r="CU16" s="1">
-        <f t="shared" si="73"/>
-        <v>177.72968547288124</v>
-      </c>
-      <c r="CV16" s="1">
-        <f t="shared" si="73"/>
-        <v>175.95238861815244</v>
-      </c>
-      <c r="CW16" s="1">
-        <f t="shared" si="73"/>
-        <v>174.19286473197093</v>
-      </c>
-      <c r="CX16" s="1">
-        <f t="shared" si="73"/>
-        <v>172.4509360846512</v>
-      </c>
-      <c r="CY16" s="1">
-        <f t="shared" si="73"/>
-        <v>170.72642672380468</v>
-      </c>
-      <c r="CZ16" s="1">
-        <f t="shared" si="73"/>
-        <v>169.01916245656662</v>
-      </c>
-      <c r="DA16" s="1">
-        <f t="shared" si="73"/>
-        <v>167.32897083200095</v>
-      </c>
-      <c r="DB16" s="1">
-        <f t="shared" si="73"/>
-        <v>165.65568112368095</v>
-      </c>
-      <c r="DC16" s="1">
-        <f t="shared" si="73"/>
-        <v>163.99912431244414</v>
-      </c>
-      <c r="DD16" s="1">
-        <f t="shared" si="73"/>
-        <v>162.35913306931968</v>
-      </c>
-      <c r="DE16" s="1">
-        <f t="shared" si="73"/>
-        <v>160.73554173862649</v>
-      </c>
-      <c r="DF16" s="1">
-        <f t="shared" si="73"/>
-        <v>159.12818632124024</v>
-      </c>
-      <c r="DG16" s="1">
-        <f t="shared" ref="DG16:FF16" si="74">DF16*(1+$AV$21)</f>
-        <v>157.53690445802783</v>
-      </c>
-      <c r="DH16" s="1">
-        <f t="shared" si="74"/>
-        <v>155.96153541344756</v>
-      </c>
-      <c r="DI16" s="1">
-        <f t="shared" si="74"/>
-        <v>154.40192005931308</v>
-      </c>
-      <c r="DJ16" s="1">
-        <f t="shared" si="74"/>
-        <v>152.85790085871994</v>
-      </c>
-      <c r="DK16" s="1">
-        <f t="shared" si="74"/>
-        <v>151.32932185013274</v>
-      </c>
-      <c r="DL16" s="1">
-        <f t="shared" si="74"/>
-        <v>149.81602863163141</v>
-      </c>
-      <c r="DM16" s="1">
-        <f t="shared" si="74"/>
-        <v>148.31786834531511</v>
-      </c>
-      <c r="DN16" s="1">
-        <f t="shared" si="74"/>
-        <v>146.83468966186194</v>
-      </c>
-      <c r="DO16" s="1">
-        <f t="shared" si="74"/>
-        <v>145.36634276524333</v>
-      </c>
-      <c r="DP16" s="1">
-        <f t="shared" si="74"/>
-        <v>143.9126793375909</v>
-      </c>
-      <c r="DQ16" s="1">
-        <f t="shared" si="74"/>
-        <v>142.47355254421498</v>
-      </c>
-      <c r="DR16" s="1">
-        <f t="shared" si="74"/>
-        <v>141.04881701877284</v>
-      </c>
-      <c r="DS16" s="1">
-        <f t="shared" si="74"/>
-        <v>139.6383288485851</v>
-      </c>
-      <c r="DT16" s="1">
-        <f t="shared" si="74"/>
-        <v>138.24194556009925</v>
-      </c>
-      <c r="DU16" s="1">
-        <f t="shared" si="74"/>
-        <v>136.85952610449826</v>
-      </c>
-      <c r="DV16" s="1">
-        <f t="shared" si="74"/>
-        <v>135.49093084345327</v>
-      </c>
-      <c r="DW16" s="1">
-        <f t="shared" si="74"/>
-        <v>134.13602153501873</v>
-      </c>
-      <c r="DX16" s="1">
-        <f t="shared" si="74"/>
-        <v>132.79466131966853</v>
-      </c>
-      <c r="DY16" s="1">
-        <f t="shared" si="74"/>
-        <v>131.46671470647186</v>
-      </c>
-      <c r="DZ16" s="1">
-        <f t="shared" si="74"/>
-        <v>130.15204755940715</v>
-      </c>
-      <c r="EA16" s="1">
-        <f t="shared" si="74"/>
-        <v>128.85052708381309</v>
-      </c>
-      <c r="EB16" s="1">
-        <f t="shared" si="74"/>
-        <v>127.56202181297496</v>
-      </c>
-      <c r="EC16" s="1">
-        <f t="shared" si="74"/>
-        <v>126.28640159484522</v>
-      </c>
-      <c r="ED16" s="1">
-        <f t="shared" si="74"/>
-        <v>125.02353757889676</v>
-      </c>
-      <c r="EE16" s="1">
-        <f t="shared" si="74"/>
-        <v>123.77330220310779</v>
-      </c>
-      <c r="EF16" s="1">
-        <f t="shared" si="74"/>
-        <v>122.53556918107671</v>
-      </c>
-      <c r="EG16" s="1">
-        <f t="shared" si="74"/>
-        <v>121.31021348926595</v>
-      </c>
-      <c r="EH16" s="1">
-        <f t="shared" si="74"/>
-        <v>120.09711135437328</v>
-      </c>
-      <c r="EI16" s="1">
-        <f t="shared" si="74"/>
-        <v>118.89614024082955</v>
-      </c>
-      <c r="EJ16" s="1">
-        <f t="shared" si="74"/>
-        <v>117.70717883842126</v>
-      </c>
-      <c r="EK16" s="1">
-        <f t="shared" si="74"/>
-        <v>116.53010705003705</v>
-      </c>
-      <c r="EL16" s="1">
-        <f t="shared" si="74"/>
-        <v>115.36480597953667</v>
-      </c>
-      <c r="EM16" s="1">
-        <f t="shared" si="74"/>
-        <v>114.2111579197413</v>
-      </c>
-      <c r="EN16" s="1">
-        <f t="shared" si="74"/>
-        <v>113.06904634054388</v>
-      </c>
-      <c r="EO16" s="1">
-        <f t="shared" si="74"/>
-        <v>111.93835587713843</v>
-      </c>
-      <c r="EP16" s="1">
-        <f t="shared" si="74"/>
-        <v>110.81897231836705</v>
-      </c>
-      <c r="EQ16" s="1">
-        <f t="shared" si="74"/>
-        <v>109.71078259518337</v>
-      </c>
-      <c r="ER16" s="1">
-        <f t="shared" si="74"/>
-        <v>108.61367476923154</v>
-      </c>
-      <c r="ES16" s="1">
-        <f t="shared" si="74"/>
-        <v>107.52753802153921</v>
-      </c>
-      <c r="ET16" s="1">
-        <f t="shared" si="74"/>
-        <v>106.45226264132383</v>
-      </c>
-      <c r="EU16" s="1">
-        <f t="shared" si="74"/>
-        <v>105.38774001491059</v>
-      </c>
-      <c r="EV16" s="1">
-        <f t="shared" si="74"/>
-        <v>104.33386261476149</v>
-      </c>
-      <c r="EW16" s="1">
-        <f t="shared" si="74"/>
-        <v>103.29052398861387</v>
-      </c>
-      <c r="EX16" s="1">
-        <f t="shared" si="74"/>
-        <v>102.25761874872774</v>
-      </c>
-      <c r="EY16" s="1">
-        <f t="shared" si="74"/>
-        <v>101.23504256124046</v>
-      </c>
-      <c r="EZ16" s="1">
-        <f t="shared" si="74"/>
-        <v>100.22269213562805</v>
-      </c>
-      <c r="FA16" s="1">
-        <f t="shared" si="74"/>
-        <v>99.220465214271769</v>
-      </c>
-      <c r="FB16" s="1">
-        <f t="shared" si="74"/>
-        <v>98.228260562129051</v>
-      </c>
-      <c r="FC16" s="1">
-        <f t="shared" si="74"/>
-        <v>97.245977956507758</v>
-      </c>
-      <c r="FD16" s="1">
-        <f t="shared" si="74"/>
-        <v>96.273518176942673</v>
-      </c>
-      <c r="FE16" s="1">
-        <f t="shared" si="74"/>
-        <v>95.310782995173241</v>
-      </c>
-      <c r="FF16" s="1">
-        <f t="shared" si="74"/>
-        <v>94.357675165221508</v>
+        <v>93.161751394735177</v>
       </c>
     </row>
     <row r="17" spans="2:50" x14ac:dyDescent="0.3">
@@ -3661,47 +3658,47 @@
         <v>60.7</v>
       </c>
       <c r="AI17" s="5">
-        <f>58.8</f>
+        <f t="shared" ref="AI17:AS17" si="74">58.8</f>
         <v>58.8</v>
       </c>
       <c r="AJ17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AK17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AL17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AM17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AN17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AO17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AP17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AQ17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AR17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
       <c r="AS17" s="5">
-        <f>58.8</f>
+        <f t="shared" si="74"/>
         <v>58.8</v>
       </c>
     </row>
@@ -3799,11 +3796,11 @@
       </c>
       <c r="Y18" s="7">
         <f t="shared" si="84"/>
-        <v>-0.17735950680272067</v>
+        <v>-1.4897959183673468</v>
       </c>
       <c r="Z18" s="7">
         <f t="shared" si="84"/>
-        <v>-0.17212739795918386</v>
+        <v>-0.10357536564625873</v>
       </c>
       <c r="AB18" s="7">
         <f>AB16/AB17</f>
@@ -3835,47 +3832,47 @@
       </c>
       <c r="AI18" s="7">
         <f t="shared" si="85"/>
-        <v>2.3568430272108838</v>
+        <v>0.82205949829931901</v>
       </c>
       <c r="AJ18" s="7">
         <f t="shared" si="85"/>
-        <v>2.984565741496596</v>
+        <v>3.0508043727891132</v>
       </c>
       <c r="AK18" s="7">
         <f t="shared" si="85"/>
-        <v>3.515127947755099</v>
+        <v>3.5866211786666646</v>
       </c>
       <c r="AL18" s="7">
         <f t="shared" si="85"/>
-        <v>3.841574418274825</v>
+        <v>3.9163347246889795</v>
       </c>
       <c r="AM18" s="7">
         <f t="shared" si="85"/>
-        <v>4.2143854465189623</v>
+        <v>4.2920432277688798</v>
       </c>
       <c r="AN18" s="7">
         <f t="shared" si="85"/>
-        <v>4.5541413872573813</v>
+        <v>4.4902800610669775</v>
       </c>
       <c r="AO18" s="7">
         <f t="shared" si="85"/>
-        <v>4.7223755274054637</v>
+        <v>4.6584886943817265</v>
       </c>
       <c r="AP18" s="7">
         <f t="shared" ref="AP18:AS18" si="86">AP16/AP17</f>
-        <v>4.8668438500239048</v>
+        <v>4.8027044475627889</v>
       </c>
       <c r="AQ18" s="7">
         <f t="shared" si="86"/>
-        <v>4.9923356153724869</v>
+        <v>4.9277544624385419</v>
       </c>
       <c r="AR18" s="7">
         <f t="shared" si="86"/>
-        <v>5.102681180225745</v>
+        <v>5.0374990652632663</v>
       </c>
       <c r="AS18" s="7">
         <f t="shared" si="86"/>
-        <v>5.2009435251089826</v>
+        <v>5.1350248599898674</v>
       </c>
     </row>
     <row r="20" spans="2:50" x14ac:dyDescent="0.3">
@@ -3960,7 +3957,7 @@
       </c>
       <c r="Y20" s="9">
         <f t="shared" ref="Y20" si="102">Y3/U3-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <v>1.5687192694919139E-2</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" ref="Z20" si="103">Z3/V3-1</f>
@@ -3993,7 +3990,7 @@
       </c>
       <c r="AI20" s="9">
         <f t="shared" si="104"/>
-        <v>-1.6699906147348731E-2</v>
+        <v>-1.026454716095726E-2</v>
       </c>
       <c r="AJ20" s="9">
         <f t="shared" si="104"/>
@@ -4013,7 +4010,7 @@
       </c>
       <c r="AN20" s="9">
         <f t="shared" si="104"/>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO20" s="9">
         <f t="shared" si="104"/>
@@ -4130,7 +4127,7 @@
       </c>
       <c r="Y21" s="9">
         <f t="shared" si="112"/>
-        <v>0.56000000000000005</v>
+        <v>0.57814661134163214</v>
       </c>
       <c r="Z21" s="9">
         <f t="shared" si="112"/>
@@ -4166,7 +4163,7 @@
       </c>
       <c r="AI21" s="9">
         <f t="shared" si="113"/>
-        <v>0.56026725048170711</v>
+        <v>0.56493095185743392</v>
       </c>
       <c r="AJ21" s="9">
         <f t="shared" si="113"/>
@@ -4178,7 +4175,7 @@
       </c>
       <c r="AL21" s="9">
         <f t="shared" si="113"/>
-        <v>0.57999999999999996</v>
+        <v>0.58000000000000007</v>
       </c>
       <c r="AM21" s="9">
         <f t="shared" si="113"/>
@@ -4198,7 +4195,7 @@
       </c>
       <c r="AQ21" s="9">
         <f t="shared" si="114"/>
-        <v>0.58000000000000007</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AR21" s="9">
         <f t="shared" si="114"/>
@@ -4309,11 +4306,11 @@
       </c>
       <c r="Y22" s="9">
         <f t="shared" si="118"/>
-        <v>5.208341906539056E-2</v>
+        <v>8.9903181189488285E-2</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" si="118"/>
-        <v>5.2665961192643891E-2</v>
+        <v>6.2665961192643893E-2</v>
       </c>
       <c r="AB22" s="9">
         <f t="shared" ref="AB22:AO22" si="119">AB10/AB3</f>
@@ -4345,47 +4342,47 @@
       </c>
       <c r="AI22" s="9">
         <f t="shared" si="119"/>
-        <v>0.1812893642659858</v>
+        <v>0.18254985921302719</v>
       </c>
       <c r="AJ22" s="9">
         <f t="shared" si="119"/>
-        <v>0.19470672686820628</v>
+        <v>0.19714692129678121</v>
       </c>
       <c r="AK22" s="9">
         <f t="shared" si="119"/>
-        <v>0.20111459166901388</v>
+        <v>0.20357814252022494</v>
       </c>
       <c r="AL22" s="9">
         <f t="shared" si="119"/>
-        <v>0.2011856229398217</v>
+        <v>0.20364871193859993</v>
       </c>
       <c r="AM22" s="9">
         <f t="shared" si="119"/>
-        <v>0.20495694114474164</v>
+        <v>0.20739550865504428</v>
       </c>
       <c r="AN22" s="9">
         <f t="shared" si="119"/>
-        <v>0.20868452661081097</v>
+        <v>0.2074463704228014</v>
       </c>
       <c r="AO22" s="9">
         <f t="shared" si="119"/>
-        <v>0.2087296983523701</v>
+        <v>0.20749169279010959</v>
       </c>
       <c r="AP22" s="9">
         <f t="shared" ref="AP22:AS22" si="120">AP10/AP3</f>
-        <v>0.20876995039930396</v>
+        <v>0.20753207905800805</v>
       </c>
       <c r="AQ22" s="9">
         <f t="shared" si="120"/>
-        <v>0.20880581855993824</v>
+        <v>0.20756806682148191</v>
       </c>
       <c r="AR22" s="9">
         <f t="shared" si="120"/>
-        <v>0.20883778028723599</v>
+        <v>0.20760013512556758</v>
       </c>
       <c r="AS22" s="9">
         <f t="shared" si="120"/>
-        <v>0.20886626103433301</v>
+        <v>0.20762871084207954</v>
       </c>
       <c r="AU22" t="s">
         <v>39</v>
@@ -4476,11 +4473,11 @@
       </c>
       <c r="Y23" s="9">
         <f t="shared" ref="Y23" si="136">Y6/U6-1</f>
-        <v>-9.5997220291865748E-4</v>
+        <v>-9.5899930507296838E-2</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" ref="Z23" si="137">Z6/V6-1</f>
-        <v>5.4549269005847556E-2</v>
+        <v>2.3533114035087399E-2</v>
       </c>
       <c r="AB23" s="9"/>
       <c r="AC23" s="9">
@@ -4556,7 +4553,7 @@
       </c>
       <c r="AV23" s="5">
         <f>NPV(AV22,AI16:FF16)</f>
-        <v>2764.3975280071254</v>
+        <v>2668.2833215883775</v>
       </c>
     </row>
     <row r="24" spans="2:50" x14ac:dyDescent="0.3">
@@ -4653,11 +4650,11 @@
       </c>
       <c r="Y24" s="9">
         <f t="shared" si="144"/>
-        <v>0.34</v>
+        <v>0.29990779160903641</v>
       </c>
       <c r="Z24" s="9">
         <f t="shared" si="144"/>
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="AB24" s="9">
         <f t="shared" ref="AB24:AS24" si="145">AB6/AB3</f>
@@ -4689,54 +4686,54 @@
       </c>
       <c r="AI24" s="9">
         <f t="shared" si="145"/>
-        <v>0.36740498589179937</v>
+        <v>0.36501608189647256</v>
       </c>
       <c r="AJ24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37460900522301116</v>
+        <v>0.37217325997287398</v>
       </c>
       <c r="AK24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37828164252911917</v>
+        <v>0.37582201742358845</v>
       </c>
       <c r="AL24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37828164252911917</v>
+        <v>0.37582201742358845</v>
       </c>
       <c r="AM24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37457299897491209</v>
+        <v>0.37213748784100426</v>
       </c>
       <c r="AN24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37090071467123648</v>
+        <v>0.37213748784100426</v>
       </c>
       <c r="AO24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37090071467123648</v>
+        <v>0.37213748784100426</v>
       </c>
       <c r="AP24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37090071467123653</v>
+        <v>0.37213748784100431</v>
       </c>
       <c r="AQ24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37090071467123653</v>
+        <v>0.37213748784100431</v>
       </c>
       <c r="AR24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37090071467123653</v>
+        <v>0.37213748784100431</v>
       </c>
       <c r="AS24" s="9">
         <f t="shared" si="145"/>
-        <v>0.37090071467123653</v>
+        <v>0.37213748784100431</v>
       </c>
       <c r="AU24" t="s">
         <v>41</v>
       </c>
       <c r="AV24" s="5">
         <f>Main!D8</f>
-        <v>-2150.2999999999997</v>
+        <v>-2248.4</v>
       </c>
     </row>
     <row r="25" spans="2:50" x14ac:dyDescent="0.3">
@@ -4833,11 +4830,11 @@
       </c>
       <c r="Y25" s="9">
         <f t="shared" si="149"/>
-        <v>0.05</v>
+        <v>21.372093023255722</v>
       </c>
       <c r="Z25" s="9">
         <f t="shared" si="149"/>
-        <v>0.05</v>
+        <v>5.000000000000001E-2</v>
       </c>
       <c r="AB25" s="9">
         <f t="shared" ref="AB25:AO25" si="150">AB14/AB13</f>
@@ -4869,7 +4866,7 @@
       </c>
       <c r="AI25" s="9">
         <f t="shared" si="150"/>
-        <v>0.15395791717744969</v>
+        <v>0.70919204139467229</v>
       </c>
       <c r="AJ25" s="9">
         <f t="shared" si="150"/>
@@ -4897,11 +4894,11 @@
       </c>
       <c r="AP25" s="9">
         <f t="shared" ref="AP25:AS25" si="151">AP14/AP13</f>
-        <v>0.19999999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="AQ25" s="9">
         <f t="shared" si="151"/>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AR25" s="9">
         <f t="shared" si="151"/>
@@ -4916,7 +4913,7 @@
       </c>
       <c r="AV25" s="5">
         <f>AV23+AV24</f>
-        <v>614.09752800712567</v>
+        <v>419.88332158837738</v>
       </c>
       <c r="AX25" t="s">
         <v>65</v>
@@ -5016,11 +5013,11 @@
       </c>
       <c r="Y26" s="9">
         <f t="shared" si="154"/>
-        <v>-2.4664199948442454E-2</v>
+        <v>-0.20193637621023511</v>
       </c>
       <c r="Z26" s="9">
         <f t="shared" si="154"/>
-        <v>-2.3853563861504012E-2</v>
+        <v>-1.4353563861504015E-2</v>
       </c>
       <c r="AB26" s="9">
         <f t="shared" ref="AB26:AO26" si="155">AB16/AB3</f>
@@ -5052,54 +5049,54 @@
       </c>
       <c r="AI26" s="9">
         <f t="shared" si="155"/>
-        <v>8.2670100755817752E-2</v>
+        <v>2.8647584811482926E-2</v>
       </c>
       <c r="AJ26" s="9">
         <f t="shared" si="155"/>
-        <v>0.10263577986598399</v>
+        <v>0.10423149108384026</v>
       </c>
       <c r="AK26" s="9">
         <f t="shared" si="155"/>
-        <v>0.11851098365586354</v>
+        <v>0.12013510360937936</v>
       </c>
       <c r="AL26" s="9">
         <f t="shared" si="155"/>
-        <v>0.12697743332213726</v>
+        <v>0.12860683495205102</v>
       </c>
       <c r="AM26" s="9">
         <f t="shared" si="155"/>
-        <v>0.13656876285386529</v>
+        <v>0.13818094628747479</v>
       </c>
       <c r="AN26" s="9">
         <f t="shared" si="155"/>
-        <v>0.1446849836282362</v>
+        <v>0.14313179915500138</v>
       </c>
       <c r="AO26" s="9">
         <f t="shared" si="155"/>
-        <v>0.14854433564444802</v>
+        <v>0.14702337006173913</v>
       </c>
       <c r="AP26" s="9">
         <f t="shared" ref="AP26:AS26" si="156">AP16/AP3</f>
-        <v>0.15157291913649526</v>
+        <v>0.15007412340876813</v>
       </c>
       <c r="AQ26" s="9">
         <f t="shared" si="156"/>
-        <v>0.15394181483336203</v>
+        <v>0.15245709488103176</v>
       </c>
       <c r="AR26" s="9">
         <f t="shared" si="156"/>
-        <v>0.15578652461839532</v>
+        <v>0.15430932971017167</v>
       </c>
       <c r="AS26" s="9">
         <f t="shared" si="156"/>
-        <v>0.15721436250687595</v>
+        <v>0.15573935900963706</v>
       </c>
       <c r="AU26" t="s">
         <v>43</v>
       </c>
       <c r="AV26" s="4">
         <f>AV25/AO17</f>
-        <v>10.443835510325266</v>
+        <v>7.1408728161288675</v>
       </c>
       <c r="AX26" t="s">
         <v>66</v>
@@ -5111,7 +5108,7 @@
       </c>
       <c r="AV27" s="4">
         <f>Main!D3</f>
-        <v>13.53</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="28" spans="2:50" x14ac:dyDescent="0.3">
@@ -5120,7 +5117,7 @@
       </c>
       <c r="AV28" s="10">
         <f>AV26/AV27-1</f>
-        <v>-0.22809789280670612</v>
+        <v>3.1918037012842237E-2</v>
       </c>
     </row>
     <row r="29" spans="2:50" x14ac:dyDescent="0.3">

--- a/Financial Analysis/PSFE.xlsx
+++ b/Financial Analysis/PSFE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64AA7C5-C399-484D-A764-ADE7B8BB3D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8E4960-0D59-4F7A-9681-C393ABD5D33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{6F8D5EDB-60E6-4055-AE62-151FC6B3FA19}"/>
   </bookViews>
@@ -229,7 +229,7 @@
     <t>maybe good to do cash flow statement</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46067</v>
       </c>
       <c r="G3" s="3">
         <v>46086</v>
@@ -1085,7 +1085,7 @@
         <v>1721.04702</v>
       </c>
       <c r="AK3" s="8">
-        <f t="shared" ref="AK3:AN3" si="0">AJ3*1.02</f>
+        <f t="shared" ref="AK3:AM3" si="0">AJ3*1.02</f>
         <v>1755.4679604</v>
       </c>
       <c r="AL3" s="8">
@@ -1196,7 +1196,7 @@
         <v>183</v>
       </c>
       <c r="Z4" s="5">
-        <f t="shared" ref="Y4:Z4" si="2">Z3-Z5</f>
+        <f t="shared" ref="Z4" si="2">Z3-Z5</f>
         <v>186.69243999999992</v>
       </c>
       <c r="AB4" s="5">
@@ -1365,7 +1365,7 @@
         <v>250.8</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Y5:Z5" si="6">Z3*0.56</f>
+        <f t="shared" ref="Z5" si="6">Z3*0.56</f>
         <v>237.60855999999995</v>
       </c>
       <c r="AB5" s="8">
@@ -2707,7 +2707,7 @@
         <v>91.9</v>
       </c>
       <c r="Z14" s="5">
-        <f t="shared" ref="Y14:Z14" si="55">Z13*0.05</f>
+        <f t="shared" ref="Z14" si="55">Z13*0.05</f>
         <v>-0.32053850000000073</v>
       </c>
       <c r="AB14" s="5">
@@ -4388,7 +4388,7 @@
         <v>39</v>
       </c>
       <c r="AV22" s="9">
-        <v>0.09</v>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="2:50" x14ac:dyDescent="0.3">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="AV23" s="5">
         <f>NPV(AV22,AI16:FF16)</f>
-        <v>2668.2833215883775</v>
+        <v>2517.6827894780131</v>
       </c>
     </row>
     <row r="24" spans="2:50" x14ac:dyDescent="0.3">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="AV25" s="5">
         <f>AV23+AV24</f>
-        <v>419.88332158837738</v>
+        <v>269.282789478013</v>
       </c>
       <c r="AX25" t="s">
         <v>65</v>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AV26" s="4">
         <f>AV25/AO17</f>
-        <v>7.1408728161288675</v>
+        <v>4.5796392768369563</v>
       </c>
       <c r="AX26" t="s">
         <v>66</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AV28" s="10">
         <f>AV26/AV27-1</f>
-        <v>3.1918037012842237E-2</v>
+        <v>-0.3382024166420583</v>
       </c>
     </row>
     <row r="29" spans="2:50" x14ac:dyDescent="0.3">
